--- a/www/flightdata/xlsx/eoss-387.xlsx
+++ b/www/flightdata/xlsx/eoss-387.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="540">
   <si>
     <t>flight</t>
   </si>
@@ -147,7 +147,7 @@
     <t>344</t>
   </si>
   <si>
-    <t>1hrs 36mins 7secs</t>
+    <t>1hrs 48mins 37secs</t>
   </si>
   <si>
     <t>flightid</t>
@@ -1332,6 +1332,12 @@
     <t>/161915h3924.91N/10228.66WO156/011/A=005090 41T8467P EOSS Balloon</t>
   </si>
   <si>
+    <t>/161945h3924.84N/10228.63WO140/007/A=004606 46T8622P EOSS Balloon</t>
+  </si>
+  <si>
+    <t>/163145h3924.76N/10228.59WO170/000/A=004206 138T8762P EOSS Balloon</t>
+  </si>
+  <si>
     <t>KC0D-2&gt;APZEOS,EOSS,WIDE2-1,qAO,N0JD-10:/153645h3949.83N/10318.10WO186/016/A=080016 13T261P EOSS Balloon</t>
   </si>
   <si>
@@ -1621,6 +1627,12 @@
   </si>
   <si>
     <t>KC0D-2&gt;APZEOS,EOSS*,WIDE2-1,qAO,W9CN-9:/161915h3924.91N/10228.66WO156/011/A=005090 41T8467P EOSS Balloon</t>
+  </si>
+  <si>
+    <t>KC0D-2&gt;APZEOS,EOSS*,WIDE2-1,qAO,W9CN-9:/161945h3924.84N/10228.63WO140/007/A=004606 46T8622P EOSS Balloon</t>
+  </si>
+  <si>
+    <t>KC0D-2&gt;APZEOS,EOSS,WIDE2-1,qAO,KE0UWC-9:/163145h3924.76N/10228.59WO170/000/A=004206 138T8762P EOSS Balloon</t>
   </si>
   <si>
     <t>n/a</t>
@@ -2127,19 +2139,19 @@
         <v>27272.59</v>
       </c>
       <c r="I2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
       </c>
       <c r="K2">
-        <v>5767</v>
+        <v>6517</v>
       </c>
       <c r="L2">
-        <v>101.55</v>
+        <v>101.7</v>
       </c>
       <c r="M2">
-        <v>163.43</v>
+        <v>163.66</v>
       </c>
       <c r="N2">
         <v>9.630000000000001</v>
@@ -2196,22 +2208,22 @@
         <v>1418.84</v>
       </c>
       <c r="AF2">
-        <v>39.4151666667</v>
+        <v>39.4126666667</v>
       </c>
       <c r="AG2">
-        <v>-102.4776666667</v>
+        <v>-102.4765</v>
       </c>
       <c r="AH2">
-        <v>101.55</v>
+        <v>101.7</v>
       </c>
       <c r="AI2">
-        <v>163.43</v>
+        <v>163.66</v>
       </c>
       <c r="AJ2">
-        <v>5090</v>
+        <v>4206</v>
       </c>
       <c r="AK2">
-        <v>1551.43</v>
+        <v>1281.99</v>
       </c>
     </row>
   </sheetData>
@@ -19272,7 +19284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU98"/>
+  <dimension ref="A1:AU100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:47">
@@ -19450,7 +19462,7 @@
         <v>341</v>
       </c>
       <c r="K2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L2">
         <v>186</v>
@@ -19507,19 +19519,19 @@
         <v>-24.03091667</v>
       </c>
       <c r="AD2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AF2">
         <v>-78.841667</v>
       </c>
       <c r="AL2">
-        <v>-78.84302700000001</v>
+        <v>-78.87849199999999</v>
       </c>
       <c r="AN2">
         <v>-24.030917</v>
       </c>
       <c r="AT2">
-        <v>-24.03134</v>
+        <v>-24.042151</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -19554,7 +19566,7 @@
         <v>342</v>
       </c>
       <c r="K3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L3">
         <v>163</v>
@@ -19611,7 +19623,7 @@
         <v>-25.68466667</v>
       </c>
       <c r="AD3" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE3">
         <v>-0.180833</v>
@@ -19629,7 +19641,7 @@
         <v>-0.707107</v>
       </c>
       <c r="AL3">
-        <v>-84.22279</v>
+        <v>-84.035376</v>
       </c>
       <c r="AM3">
         <v>-0.055125</v>
@@ -19647,7 +19659,7 @@
         <v>-0.707106</v>
       </c>
       <c r="AT3">
-        <v>-25.671228</v>
+        <v>-25.614101</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -19682,7 +19694,7 @@
         <v>343</v>
       </c>
       <c r="K4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L4">
         <v>136</v>
@@ -19739,7 +19751,7 @@
         <v>-25.17633333</v>
       </c>
       <c r="AD4" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE4">
         <v>0.055556</v>
@@ -19763,7 +19775,7 @@
         <v>0.707105</v>
       </c>
       <c r="AL4">
-        <v>-82.979866</v>
+        <v>-83.263727</v>
       </c>
       <c r="AM4">
         <v>0.016944</v>
@@ -19787,7 +19799,7 @@
         <v>0.707104</v>
       </c>
       <c r="AT4">
-        <v>-25.292287</v>
+        <v>-25.378812</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -19822,7 +19834,7 @@
         <v>344</v>
       </c>
       <c r="K5" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L5">
         <v>140</v>
@@ -19879,7 +19891,7 @@
         <v>-24.14033333</v>
       </c>
       <c r="AD5" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE5">
         <v>0.113333</v>
@@ -19903,7 +19915,7 @@
         <v>0.7526929999999999</v>
       </c>
       <c r="AL5">
-        <v>-77.95558</v>
+        <v>-77.985331</v>
       </c>
       <c r="AM5">
         <v>0.034533</v>
@@ -19927,7 +19939,7 @@
         <v>0.752484</v>
       </c>
       <c r="AT5">
-        <v>-23.760869</v>
+        <v>-23.769937</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -19962,7 +19974,7 @@
         <v>345</v>
       </c>
       <c r="K6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L6">
         <v>229</v>
@@ -20019,7 +20031,7 @@
         <v>-21.92533333</v>
       </c>
       <c r="AD6" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE6">
         <v>0.242222</v>
@@ -20043,7 +20055,7 @@
         <v>1.042908</v>
       </c>
       <c r="AL6">
-        <v>-73.100436</v>
+        <v>-72.906808</v>
       </c>
       <c r="AM6">
         <v>0.073833</v>
@@ -20067,7 +20079,7 @@
         <v>1.042931</v>
       </c>
       <c r="AT6">
-        <v>-22.281037</v>
+        <v>-22.222017</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -20102,7 +20114,7 @@
         <v>346</v>
       </c>
       <c r="K7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L7">
         <v>194</v>
@@ -20159,7 +20171,7 @@
         <v>-20.74666667</v>
       </c>
       <c r="AD7" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE7">
         <v>0.128889</v>
@@ -20183,7 +20195,7 @@
         <v>0.364303</v>
       </c>
       <c r="AL7">
-        <v>-69.150603</v>
+        <v>-68.983672</v>
       </c>
       <c r="AM7">
         <v>0.039289</v>
@@ -20207,7 +20219,7 @@
         <v>0.364349</v>
       </c>
       <c r="AT7">
-        <v>-21.07713</v>
+        <v>-21.026247</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -20242,7 +20254,7 @@
         <v>347</v>
       </c>
       <c r="K8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L8">
         <v>70</v>
@@ -20299,7 +20311,7 @@
         <v>-20.452</v>
       </c>
       <c r="AD8" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE8">
         <v>0.032222</v>
@@ -20323,7 +20335,7 @@
         <v>-0.234092</v>
       </c>
       <c r="AL8">
-        <v>-65.675911</v>
+        <v>-65.676137</v>
       </c>
       <c r="AM8">
         <v>0.009821999999999999</v>
@@ -20347,7 +20359,7 @@
         <v>-0.234069</v>
       </c>
       <c r="AT8">
-        <v>-20.018024</v>
+        <v>-20.018093</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -20382,7 +20394,7 @@
         <v>348</v>
       </c>
       <c r="K9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L9">
         <v>161</v>
@@ -20439,7 +20451,7 @@
         <v>-19.38533333</v>
       </c>
       <c r="AD9" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE9">
         <v>0.116667</v>
@@ -20463,7 +20475,7 @@
         <v>0.338654</v>
       </c>
       <c r="AL9">
-        <v>-62.347226</v>
+        <v>-62.487933</v>
       </c>
       <c r="AM9">
         <v>0.035556</v>
@@ -20487,7 +20499,7 @@
         <v>0.338533</v>
       </c>
       <c r="AT9">
-        <v>-19.003408</v>
+        <v>-19.046298</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -20522,7 +20534,7 @@
         <v>349</v>
       </c>
       <c r="K10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L10">
         <v>41</v>
@@ -20579,7 +20591,7 @@
         <v>-18.01366667</v>
       </c>
       <c r="AD10" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE10">
         <v>0.15</v>
@@ -20603,7 +20615,7 @@
         <v>0.548091</v>
       </c>
       <c r="AL10">
-        <v>-58.989134</v>
+        <v>-59.16611</v>
       </c>
       <c r="AM10">
         <v>0.045722</v>
@@ -20627,7 +20639,7 @@
         <v>0.548109</v>
       </c>
       <c r="AT10">
-        <v>-17.979844</v>
+        <v>-18.033789</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -20662,7 +20674,7 @@
         <v>350</v>
       </c>
       <c r="K11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L11">
         <v>84</v>
@@ -20719,7 +20731,7 @@
         <v>-16.36766667</v>
       </c>
       <c r="AD11" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE11">
         <v>0.18</v>
@@ -20743,7 +20755,7 @@
         <v>0.723314</v>
       </c>
       <c r="AL11">
-        <v>-55.702069</v>
+        <v>-55.827605</v>
       </c>
       <c r="AM11">
         <v>0.054867</v>
@@ -20767,7 +20779,7 @@
         <v>0.723357</v>
       </c>
       <c r="AT11">
-        <v>-16.977948</v>
+        <v>-17.016213</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -20802,7 +20814,7 @@
         <v>351</v>
       </c>
       <c r="K12" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L12">
         <v>179</v>
@@ -20859,7 +20871,7 @@
         <v>-15.88</v>
       </c>
       <c r="AD12" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE12">
         <v>0.053333</v>
@@ -20883,7 +20895,7 @@
         <v>-0.314239</v>
       </c>
       <c r="AL12">
-        <v>-52.405166</v>
+        <v>-52.434269</v>
       </c>
       <c r="AM12">
         <v>0.016256</v>
@@ -20907,7 +20919,7 @@
         <v>-0.314226</v>
       </c>
       <c r="AT12">
-        <v>-15.973065</v>
+        <v>-15.981936</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -20942,7 +20954,7 @@
         <v>352</v>
       </c>
       <c r="K13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L13">
         <v>147</v>
@@ -20999,7 +21011,7 @@
         <v>-15.11833333</v>
       </c>
       <c r="AD13" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE13">
         <v>0.083333</v>
@@ -21023,7 +21035,7 @@
         <v>-0.04882</v>
       </c>
       <c r="AL13">
-        <v>-49.314215</v>
+        <v>-49.247092</v>
       </c>
       <c r="AM13">
         <v>0.025389</v>
@@ -21047,7 +21059,7 @@
         <v>-0.049128</v>
       </c>
       <c r="AT13">
-        <v>-15.030942</v>
+        <v>-15.010481</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -21082,7 +21094,7 @@
         <v>353</v>
       </c>
       <c r="K14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L14">
         <v>147</v>
@@ -21139,7 +21151,7 @@
         <v>-14.112</v>
       </c>
       <c r="AD14" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE14">
         <v>0.11</v>
@@ -21163,7 +21175,7 @@
         <v>0.189859</v>
       </c>
       <c r="AL14">
-        <v>-46.599457</v>
+        <v>-46.467669</v>
       </c>
       <c r="AM14">
         <v>0.033544</v>
@@ -21187,7 +21199,7 @@
         <v>0.190355</v>
       </c>
       <c r="AT14">
-        <v>-14.203515</v>
+        <v>-14.163344</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -21222,7 +21234,7 @@
         <v>354</v>
       </c>
       <c r="K15" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L15">
         <v>118</v>
@@ -21279,7 +21291,7 @@
         <v>-13.401</v>
       </c>
       <c r="AD15" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE15">
         <v>0.077778</v>
@@ -21303,7 +21315,7 @@
         <v>-0.117708</v>
       </c>
       <c r="AL15">
-        <v>-44.26307</v>
+        <v>-44.107728</v>
       </c>
       <c r="AM15">
         <v>0.0237</v>
@@ -21327,7 +21339,7 @@
         <v>-0.117916</v>
       </c>
       <c r="AT15">
-        <v>-13.4914</v>
+        <v>-13.44405</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -21362,7 +21374,7 @@
         <v>355</v>
       </c>
       <c r="K16" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L16">
         <v>105</v>
@@ -21419,7 +21431,7 @@
         <v>-13.10666667</v>
       </c>
       <c r="AD16" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE16">
         <v>0.032222</v>
@@ -21443,7 +21455,7 @@
         <v>-0.551718</v>
       </c>
       <c r="AL16">
-        <v>-42.255893</v>
+        <v>-42.116559</v>
       </c>
       <c r="AM16">
         <v>0.009811</v>
@@ -21467,7 +21479,7 @@
         <v>-0.552</v>
       </c>
       <c r="AT16">
-        <v>-12.879612</v>
+        <v>-12.837141</v>
       </c>
     </row>
     <row r="17" spans="1:46">
@@ -21502,7 +21514,7 @@
         <v>356</v>
       </c>
       <c r="K17" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L17">
         <v>125</v>
@@ -21559,7 +21571,7 @@
         <v>-12.54733333</v>
       </c>
       <c r="AD17" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE17">
         <v>0.061111</v>
@@ -21583,7 +21595,7 @@
         <v>-0.243181</v>
       </c>
       <c r="AL17">
-        <v>-40.606554</v>
+        <v>-40.513168</v>
       </c>
       <c r="AM17">
         <v>0.018644</v>
@@ -21607,7 +21619,7 @@
         <v>-0.242564</v>
       </c>
       <c r="AT17">
-        <v>-12.37691</v>
+        <v>-12.348445</v>
       </c>
     </row>
     <row r="18" spans="1:46">
@@ -21642,7 +21654,7 @@
         <v>357</v>
       </c>
       <c r="K18" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L18">
         <v>120</v>
@@ -21699,7 +21711,7 @@
         <v>-12.436</v>
       </c>
       <c r="AD18" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE18">
         <v>0.012222</v>
@@ -21723,7 +21735,7 @@
         <v>-0.731867</v>
       </c>
       <c r="AL18">
-        <v>-39.222181</v>
+        <v>-39.192722</v>
       </c>
       <c r="AM18">
         <v>0.003711</v>
@@ -21747,7 +21759,7 @@
         <v>-0.732297</v>
       </c>
       <c r="AT18">
-        <v>-11.954949</v>
+        <v>-11.94597</v>
       </c>
     </row>
     <row r="19" spans="1:46">
@@ -21782,7 +21794,7 @@
         <v>358</v>
       </c>
       <c r="K19" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L19">
         <v>102</v>
@@ -21839,7 +21851,7 @@
         <v>-11.88733333</v>
       </c>
       <c r="AD19" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE19">
         <v>0.06</v>
@@ -21863,7 +21875,7 @@
         <v>-0.204058</v>
       </c>
       <c r="AL19">
-        <v>-38.101259</v>
+        <v>-38.137175</v>
       </c>
       <c r="AM19">
         <v>0.018289</v>
@@ -21887,7 +21899,7 @@
         <v>-0.20399</v>
       </c>
       <c r="AT19">
-        <v>-11.613285</v>
+        <v>-11.624234</v>
       </c>
     </row>
     <row r="20" spans="1:46">
@@ -21922,7 +21934,7 @@
         <v>359</v>
       </c>
       <c r="K20" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -21979,7 +21991,7 @@
         <v>-11.03366667</v>
       </c>
       <c r="AD20" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE20">
         <v>0.093333</v>
@@ -22003,7 +22015,7 @@
         <v>0.16662</v>
       </c>
       <c r="AL20">
-        <v>-37.201341</v>
+        <v>-37.290746</v>
       </c>
       <c r="AM20">
         <v>0.028456</v>
@@ -22027,7 +22039,7 @@
         <v>0.166908</v>
       </c>
       <c r="AT20">
-        <v>-11.338987</v>
+        <v>-11.366239</v>
       </c>
     </row>
     <row r="21" spans="1:46">
@@ -22062,7 +22074,7 @@
         <v>360</v>
       </c>
       <c r="K21" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L21">
         <v>121</v>
@@ -22119,7 +22131,7 @@
         <v>-10.88133333</v>
       </c>
       <c r="AD21" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE21">
         <v>0.016667</v>
@@ -22143,7 +22155,7 @@
         <v>-0.694296</v>
       </c>
       <c r="AL21">
-        <v>-36.40851</v>
+        <v>-36.535545</v>
       </c>
       <c r="AM21">
         <v>0.005078</v>
@@ -22167,7 +22179,7 @@
         <v>-0.694285</v>
       </c>
       <c r="AT21">
-        <v>-11.097326</v>
+        <v>-11.136048</v>
       </c>
     </row>
     <row r="22" spans="1:46">
@@ -22202,7 +22214,7 @@
         <v>361</v>
       </c>
       <c r="K22" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L22">
         <v>128</v>
@@ -22259,7 +22271,7 @@
         <v>-10.71866667</v>
       </c>
       <c r="AD22" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE22">
         <v>0.017778</v>
@@ -22283,7 +22295,7 @@
         <v>-0.656907</v>
       </c>
       <c r="AL22">
-        <v>-35.683457</v>
+        <v>-35.827562</v>
       </c>
       <c r="AM22">
         <v>0.005422</v>
@@ -22307,7 +22319,7 @@
         <v>-0.656704</v>
       </c>
       <c r="AT22">
-        <v>-10.876324</v>
+        <v>-10.920249</v>
       </c>
     </row>
     <row r="23" spans="1:46">
@@ -22342,7 +22354,7 @@
         <v>362</v>
       </c>
       <c r="K23" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L23">
         <v>116</v>
@@ -22399,7 +22411,7 @@
         <v>-10.15</v>
       </c>
       <c r="AD23" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE23">
         <v>0.062222</v>
@@ -22423,7 +22435,7 @@
         <v>-0.123269</v>
       </c>
       <c r="AL23">
-        <v>-35.018554</v>
+        <v>-35.158521</v>
       </c>
       <c r="AM23">
         <v>0.018956</v>
@@ -22447,7 +22459,7 @@
         <v>-0.123614</v>
       </c>
       <c r="AT23">
-        <v>-10.67365</v>
+        <v>-10.716314</v>
       </c>
     </row>
     <row r="24" spans="1:46">
@@ -22482,7 +22494,7 @@
         <v>363</v>
       </c>
       <c r="K24" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L24">
         <v>114</v>
@@ -22539,7 +22551,7 @@
         <v>-10.18033333</v>
       </c>
       <c r="AD24" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE24">
         <v>-0.003333</v>
@@ -22563,7 +22575,7 @@
         <v>-0.887807</v>
       </c>
       <c r="AL24">
-        <v>-34.349126</v>
+        <v>-34.465909</v>
       </c>
       <c r="AM24">
         <v>-0.001011</v>
@@ -22587,7 +22599,7 @@
         <v>-0.887548</v>
       </c>
       <c r="AT24">
-        <v>-10.469601</v>
+        <v>-10.505198</v>
       </c>
     </row>
     <row r="25" spans="1:46">
@@ -22622,7 +22634,7 @@
         <v>364</v>
       </c>
       <c r="K25" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L25">
         <v>121</v>
@@ -22679,7 +22691,7 @@
         <v>-10.414</v>
       </c>
       <c r="AD25" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE25">
         <v>-0.025556</v>
@@ -22703,7 +22715,7 @@
         <v>-1.10341</v>
       </c>
       <c r="AL25">
-        <v>-33.643453</v>
+        <v>-33.720221</v>
       </c>
       <c r="AM25">
         <v>-0.007789</v>
@@ -22727,7 +22739,7 @@
         <v>-1.103299</v>
       </c>
       <c r="AT25">
-        <v>-10.254506</v>
+        <v>-10.277906</v>
       </c>
     </row>
     <row r="26" spans="1:46">
@@ -22762,7 +22774,7 @@
         <v>365</v>
       </c>
       <c r="K26" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L26">
         <v>106</v>
@@ -22819,7 +22831,7 @@
         <v>-9.967000000000001</v>
       </c>
       <c r="AD26" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE26">
         <v>0.048889</v>
@@ -22843,7 +22855,7 @@
         <v>-0.189711</v>
       </c>
       <c r="AL26">
-        <v>-32.937423</v>
+        <v>-32.965625</v>
       </c>
       <c r="AM26">
         <v>0.0149</v>
@@ -22867,7 +22879,7 @@
         <v>-0.189737</v>
       </c>
       <c r="AT26">
-        <v>-10.039304</v>
+        <v>-10.0479</v>
       </c>
     </row>
     <row r="27" spans="1:46">
@@ -22902,7 +22914,7 @@
         <v>366</v>
       </c>
       <c r="K27" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L27">
         <v>118</v>
@@ -22959,7 +22971,7 @@
         <v>-9.99733333</v>
       </c>
       <c r="AD27" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE27">
         <v>-0.003333</v>
@@ -22983,7 +22995,7 @@
         <v>-0.813397</v>
       </c>
       <c r="AL27">
-        <v>-32.194725</v>
+        <v>-32.17043</v>
       </c>
       <c r="AM27">
         <v>-0.001011</v>
@@ -23007,7 +23019,7 @@
         <v>-0.813111</v>
       </c>
       <c r="AT27">
-        <v>-9.81293</v>
+        <v>-9.805524</v>
       </c>
     </row>
     <row r="28" spans="1:46">
@@ -23042,7 +23054,7 @@
         <v>367</v>
       </c>
       <c r="K28" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="L28">
         <v>112</v>
@@ -23099,7 +23111,7 @@
         <v>-10.028</v>
       </c>
       <c r="AD28" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE28">
         <v>-0.003333</v>
@@ -23123,7 +23135,7 @@
         <v>-0.787869</v>
       </c>
       <c r="AL28">
-        <v>-31.41638</v>
+        <v>-31.342354</v>
       </c>
       <c r="AM28">
         <v>-0.001022</v>
@@ -23147,7 +23159,7 @@
         <v>-0.788022</v>
       </c>
       <c r="AT28">
-        <v>-9.575689000000001</v>
+        <v>-9.553124</v>
       </c>
     </row>
     <row r="29" spans="1:46">
@@ -23182,7 +23194,7 @@
         <v>368</v>
       </c>
       <c r="K29" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L29">
         <v>98</v>
@@ -23239,7 +23251,7 @@
         <v>-9.50966667</v>
       </c>
       <c r="AD29" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE29">
         <v>0.056667</v>
@@ -23263,7 +23275,7 @@
         <v>-0.027758</v>
       </c>
       <c r="AL29">
-        <v>-30.652881</v>
+        <v>-30.540232</v>
       </c>
       <c r="AM29">
         <v>0.017278</v>
@@ -23287,7 +23299,7 @@
         <v>-0.027488</v>
       </c>
       <c r="AT29">
-        <v>-9.342978</v>
+        <v>-9.308641</v>
       </c>
     </row>
     <row r="30" spans="1:46">
@@ -23322,7 +23334,7 @@
         <v>369</v>
       </c>
       <c r="K30" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L30">
         <v>115</v>
@@ -23379,7 +23391,7 @@
         <v>-9.276</v>
       </c>
       <c r="AD30" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE30">
         <v>0.025556</v>
@@ -23403,7 +23415,7 @@
         <v>-0.420536</v>
       </c>
       <c r="AL30">
-        <v>-29.89232</v>
+        <v>-29.754453</v>
       </c>
       <c r="AM30">
         <v>0.007789</v>
@@ -23427,7 +23439,7 @@
         <v>-0.420509</v>
       </c>
       <c r="AT30">
-        <v>-9.111164</v>
+        <v>-9.069140000000001</v>
       </c>
     </row>
     <row r="31" spans="1:46">
@@ -23462,7 +23474,7 @@
         <v>370</v>
       </c>
       <c r="K31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L31">
         <v>107</v>
@@ -23519,7 +23531,7 @@
         <v>-9.022</v>
       </c>
       <c r="AD31" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE31">
         <v>0.027778</v>
@@ -23543,7 +23555,7 @@
         <v>-0.383792</v>
       </c>
       <c r="AL31">
-        <v>-29.146566</v>
+        <v>-28.998794</v>
       </c>
       <c r="AM31">
         <v>0.008467000000000001</v>
@@ -23567,7 +23579,7 @@
         <v>-0.383759</v>
       </c>
       <c r="AT31">
-        <v>-8.883864000000001</v>
+        <v>-8.838820999999999</v>
       </c>
     </row>
     <row r="32" spans="1:46">
@@ -23602,7 +23614,7 @@
         <v>371</v>
       </c>
       <c r="K32" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="L32">
         <v>108</v>
@@ -23659,7 +23671,7 @@
         <v>-8.625999999999999</v>
       </c>
       <c r="AD32" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE32">
         <v>0.043333</v>
@@ -23683,7 +23695,7 @@
         <v>-0.173692</v>
       </c>
       <c r="AL32">
-        <v>-28.436669</v>
+        <v>-28.29408</v>
       </c>
       <c r="AM32">
         <v>0.0132</v>
@@ -23707,7 +23719,7 @@
         <v>-0.174042</v>
       </c>
       <c r="AT32">
-        <v>-8.667486999999999</v>
+        <v>-8.624025</v>
       </c>
     </row>
     <row r="33" spans="1:46">
@@ -23742,7 +23754,7 @@
         <v>372</v>
       </c>
       <c r="K33" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L33">
         <v>107</v>
@@ -23799,7 +23811,7 @@
         <v>-8.199</v>
       </c>
       <c r="AD33" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE33">
         <v>0.046667</v>
@@ -23823,7 +23835,7 @@
         <v>-0.126482</v>
       </c>
       <c r="AL33">
-        <v>-27.772165</v>
+        <v>-27.647541</v>
       </c>
       <c r="AM33">
         <v>0.014233</v>
@@ -23847,7 +23859,7 @@
         <v>-0.126101</v>
       </c>
       <c r="AT33">
-        <v>-8.464953</v>
+        <v>-8.426966</v>
       </c>
     </row>
     <row r="34" spans="1:46">
@@ -23882,7 +23894,7 @@
         <v>373</v>
       </c>
       <c r="K34" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L34">
         <v>111</v>
@@ -23939,7 +23951,7 @@
         <v>-8.128</v>
       </c>
       <c r="AD34" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE34">
         <v>0.007778</v>
@@ -23963,7 +23975,7 @@
         <v>-0.647413</v>
       </c>
       <c r="AL34">
-        <v>-27.129718</v>
+        <v>-27.034078</v>
       </c>
       <c r="AM34">
         <v>0.002367</v>
@@ -23987,7 +23999,7 @@
         <v>-0.647558</v>
       </c>
       <c r="AT34">
-        <v>-8.269138999999999</v>
+        <v>-8.239986999999999</v>
       </c>
     </row>
     <row r="35" spans="1:46">
@@ -24022,7 +24034,7 @@
         <v>374</v>
       </c>
       <c r="K35" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L35">
         <v>104</v>
@@ -24079,7 +24091,7 @@
         <v>-8.22966667</v>
       </c>
       <c r="AD35" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE35">
         <v>-0.011111</v>
@@ -24103,7 +24115,7 @@
         <v>-0.885152</v>
       </c>
       <c r="AL35">
-        <v>-26.501306</v>
+        <v>-26.443954</v>
       </c>
       <c r="AM35">
         <v>-0.003389</v>
@@ -24127,7 +24139,7 @@
         <v>-0.885178</v>
       </c>
       <c r="AT35">
-        <v>-8.077601</v>
+        <v>-8.06012</v>
       </c>
     </row>
     <row r="36" spans="1:46">
@@ -24162,7 +24174,7 @@
         <v>375</v>
       </c>
       <c r="K36" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L36">
         <v>114</v>
@@ -24219,7 +24231,7 @@
         <v>-7.91466667</v>
       </c>
       <c r="AD36" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE36">
         <v>0.034444</v>
@@ -24243,7 +24255,7 @@
         <v>-0.246081</v>
       </c>
       <c r="AL36">
-        <v>-25.922081</v>
+        <v>-25.907004</v>
       </c>
       <c r="AM36">
         <v>0.0105</v>
@@ -24267,7 +24279,7 @@
         <v>-0.245985</v>
       </c>
       <c r="AT36">
-        <v>-7.901055</v>
+        <v>-7.89646</v>
       </c>
     </row>
     <row r="37" spans="1:46">
@@ -24302,7 +24314,7 @@
         <v>376</v>
       </c>
       <c r="K37" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L37">
         <v>115</v>
@@ -24359,7 +24371,7 @@
         <v>-7.559</v>
       </c>
       <c r="AD37" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE37">
         <v>0.038889</v>
@@ -24383,7 +24395,7 @@
         <v>-0.180549</v>
       </c>
       <c r="AL37">
-        <v>-25.39466</v>
+        <v>-25.421734</v>
       </c>
       <c r="AM37">
         <v>0.011856</v>
@@ -24407,7 +24419,7 @@
         <v>-0.18044</v>
       </c>
       <c r="AT37">
-        <v>-7.7403</v>
+        <v>-7.748553</v>
       </c>
     </row>
     <row r="38" spans="1:46">
@@ -24442,7 +24454,7 @@
         <v>377</v>
       </c>
       <c r="K38" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L38">
         <v>111</v>
@@ -24499,7 +24511,7 @@
         <v>-7.53866667</v>
       </c>
       <c r="AD38" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE38">
         <v>0.002222</v>
@@ -24523,7 +24535,7 @@
         <v>-0.692309</v>
       </c>
       <c r="AL38">
-        <v>-24.895441</v>
+        <v>-24.962994</v>
       </c>
       <c r="AM38">
         <v>0.000678</v>
@@ -24547,7 +24559,7 @@
         <v>-0.692235</v>
       </c>
       <c r="AT38">
-        <v>-7.58814</v>
+        <v>-7.608731</v>
       </c>
     </row>
     <row r="39" spans="1:46">
@@ -24582,7 +24594,7 @@
         <v>378</v>
       </c>
       <c r="K39" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L39">
         <v>108</v>
@@ -24639,7 +24651,7 @@
         <v>-7.56933333</v>
       </c>
       <c r="AD39" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE39">
         <v>-0.003333</v>
@@ -24663,7 +24675,7 @@
         <v>-0.7561600000000001</v>
       </c>
       <c r="AL39">
-        <v>-24.421956</v>
+        <v>-24.525338</v>
       </c>
       <c r="AM39">
         <v>-0.001022</v>
@@ -24687,7 +24699,7 @@
         <v>-0.75637</v>
       </c>
       <c r="AT39">
-        <v>-7.44382</v>
+        <v>-7.475333</v>
       </c>
     </row>
     <row r="40" spans="1:46">
@@ -24722,7 +24734,7 @@
         <v>379</v>
       </c>
       <c r="K40" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L40">
         <v>109</v>
@@ -24779,7 +24791,7 @@
         <v>-7.20333333</v>
       </c>
       <c r="AD40" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE40">
         <v>0.04</v>
@@ -24803,7 +24815,7 @@
         <v>-0.124246</v>
       </c>
       <c r="AL40">
-        <v>-23.997298</v>
+        <v>-24.127539</v>
       </c>
       <c r="AM40">
         <v>0.0122</v>
@@ -24827,7 +24839,7 @@
         <v>-0.123857</v>
       </c>
       <c r="AT40">
-        <v>-7.314386</v>
+        <v>-7.354086</v>
       </c>
     </row>
     <row r="41" spans="1:46">
@@ -24862,7 +24874,7 @@
         <v>380</v>
       </c>
       <c r="K41" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L41">
         <v>109</v>
@@ -24919,7 +24931,7 @@
         <v>-7.00033333</v>
       </c>
       <c r="AD41" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE41">
         <v>0.022222</v>
@@ -24943,7 +24955,7 @@
         <v>-0.380729</v>
       </c>
       <c r="AL41">
-        <v>-23.608505</v>
+        <v>-23.755957</v>
       </c>
       <c r="AM41">
         <v>0.006767</v>
@@ -24967,7 +24979,7 @@
         <v>-0.381011</v>
       </c>
       <c r="AT41">
-        <v>-7.19588</v>
+        <v>-7.240825</v>
       </c>
     </row>
     <row r="42" spans="1:46">
@@ -25002,7 +25014,7 @@
         <v>381</v>
       </c>
       <c r="K42" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L42">
         <v>110</v>
@@ -25059,7 +25071,7 @@
         <v>-6.94933333</v>
       </c>
       <c r="AD42" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE42">
         <v>0.005556</v>
@@ -25083,7 +25095,7 @@
         <v>-0.618387</v>
       </c>
       <c r="AL42">
-        <v>-23.245175</v>
+        <v>-23.399546</v>
       </c>
       <c r="AM42">
         <v>0.0017</v>
@@ -25107,7 +25119,7 @@
         <v>-0.618036</v>
       </c>
       <c r="AT42">
-        <v>-7.085138</v>
+        <v>-7.132192</v>
       </c>
     </row>
     <row r="43" spans="1:46">
@@ -25142,7 +25154,7 @@
         <v>382</v>
       </c>
       <c r="K43" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L43">
         <v>116</v>
@@ -25199,7 +25211,7 @@
         <v>-6.97</v>
       </c>
       <c r="AD43" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE43">
         <v>-0.002222</v>
@@ -25223,7 +25235,7 @@
         <v>-0.7216399999999999</v>
       </c>
       <c r="AL43">
-        <v>-22.902624</v>
+        <v>-23.05291</v>
       </c>
       <c r="AM43">
         <v>-0.0006890000000000001</v>
@@ -25247,7 +25259,7 @@
         <v>-0.722151</v>
       </c>
       <c r="AT43">
-        <v>-6.980724</v>
+        <v>-7.026533</v>
       </c>
     </row>
     <row r="44" spans="1:46">
@@ -25282,7 +25294,7 @@
         <v>383</v>
       </c>
       <c r="K44" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L44">
         <v>121</v>
@@ -25339,7 +25351,7 @@
         <v>-6.89866667</v>
       </c>
       <c r="AD44" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE44">
         <v>0.007778</v>
@@ -25363,7 +25375,7 @@
         <v>-0.561558</v>
       </c>
       <c r="AL44">
-        <v>-22.584244</v>
+        <v>-22.719492</v>
       </c>
       <c r="AM44">
         <v>0.002378</v>
@@ -25387,7 +25399,7 @@
         <v>-0.561146</v>
       </c>
       <c r="AT44">
-        <v>-6.88368</v>
+        <v>-6.924905</v>
       </c>
     </row>
     <row r="45" spans="1:46">
@@ -25422,7 +25434,7 @@
         <v>384</v>
       </c>
       <c r="K45" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L45">
         <v>118</v>
@@ -25479,7 +25491,7 @@
         <v>-6.82733333</v>
       </c>
       <c r="AD45" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE45">
         <v>0.007778</v>
@@ -25503,7 +25515,7 @@
         <v>-0.55307</v>
       </c>
       <c r="AL45">
-        <v>-22.288591</v>
+        <v>-22.398804</v>
       </c>
       <c r="AM45">
         <v>0.002378</v>
@@ -25527,7 +25539,7 @@
         <v>-0.5526529999999999</v>
       </c>
       <c r="AT45">
-        <v>-6.793566</v>
+        <v>-6.82716</v>
       </c>
     </row>
     <row r="46" spans="1:46">
@@ -25562,7 +25574,7 @@
         <v>385</v>
       </c>
       <c r="K46" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L46">
         <v>116</v>
@@ -25619,7 +25631,7 @@
         <v>-6.77666667</v>
       </c>
       <c r="AD46" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE46">
         <v>0.005556</v>
@@ -25643,7 +25655,7 @@
         <v>-0.578359</v>
       </c>
       <c r="AL46">
-        <v>-22.013571</v>
+        <v>-22.090273</v>
       </c>
       <c r="AM46">
         <v>0.001689</v>
@@ -25667,7 +25679,7 @@
         <v>-0.57853</v>
       </c>
       <c r="AT46">
-        <v>-6.70974</v>
+        <v>-6.733119</v>
       </c>
     </row>
     <row r="47" spans="1:46">
@@ -25702,7 +25714,7 @@
         <v>386</v>
       </c>
       <c r="K47" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L47">
         <v>117</v>
@@ -25759,7 +25771,7 @@
         <v>-6.736</v>
       </c>
       <c r="AD47" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE47">
         <v>0.004444</v>
@@ -25783,7 +25795,7 @@
         <v>-0.586728</v>
       </c>
       <c r="AL47">
-        <v>-21.757838</v>
+        <v>-21.794646</v>
       </c>
       <c r="AM47">
         <v>0.001356</v>
@@ -25807,7 +25819,7 @@
         <v>-0.5865939999999999</v>
       </c>
       <c r="AT47">
-        <v>-6.631792</v>
+        <v>-6.643012</v>
       </c>
     </row>
     <row r="48" spans="1:46">
@@ -25842,7 +25854,7 @@
         <v>387</v>
       </c>
       <c r="K48" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L48">
         <v>128</v>
@@ -25899,7 +25911,7 @@
         <v>-6.777</v>
       </c>
       <c r="AD48" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE48">
         <v>-0.004444</v>
@@ -25923,7 +25935,7 @@
         <v>-0.713557</v>
       </c>
       <c r="AL48">
-        <v>-21.517856</v>
+        <v>-21.510469</v>
       </c>
       <c r="AM48">
         <v>-0.001367</v>
@@ -25947,7 +25959,7 @@
         <v>-0.714139</v>
       </c>
       <c r="AT48">
-        <v>-6.558642</v>
+        <v>-6.556389</v>
       </c>
     </row>
     <row r="49" spans="1:46">
@@ -25982,7 +25994,7 @@
         <v>388</v>
       </c>
       <c r="K49" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L49">
         <v>130</v>
@@ -26039,7 +26051,7 @@
         <v>-6.38033333</v>
       </c>
       <c r="AD49" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE49">
         <v>0.043333</v>
@@ -26063,7 +26075,7 @@
         <v>0.035909</v>
       </c>
       <c r="AL49">
-        <v>-21.307413</v>
+        <v>-21.257403</v>
       </c>
       <c r="AM49">
         <v>0.013222</v>
@@ -26087,7 +26099,7 @@
         <v>0.036648</v>
       </c>
       <c r="AT49">
-        <v>-6.4945</v>
+        <v>-6.479256</v>
       </c>
     </row>
     <row r="50" spans="1:46">
@@ -26122,7 +26134,7 @@
         <v>389</v>
       </c>
       <c r="K50" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L50">
         <v>126</v>
@@ -26179,7 +26191,7 @@
         <v>-6.44133333</v>
       </c>
       <c r="AD50" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE50">
         <v>-0.006667</v>
@@ -26203,7 +26215,7 @@
         <v>-0.745177</v>
       </c>
       <c r="AL50">
-        <v>-21.109869</v>
+        <v>-21.018712</v>
       </c>
       <c r="AM50">
         <v>-0.002033</v>
@@ -26227,7 +26239,7 @@
         <v>-0.745188</v>
       </c>
       <c r="AT50">
-        <v>-6.434289</v>
+        <v>-6.406503</v>
       </c>
     </row>
     <row r="51" spans="1:46">
@@ -26262,7 +26274,7 @@
         <v>390</v>
       </c>
       <c r="K51" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L51">
         <v>121</v>
@@ -26319,7 +26331,7 @@
         <v>-6.63466667</v>
       </c>
       <c r="AD51" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE51">
         <v>-0.021111</v>
@@ -26343,7 +26355,7 @@
         <v>-0.956239</v>
       </c>
       <c r="AL51">
-        <v>-20.921589</v>
+        <v>-20.793113</v>
       </c>
       <c r="AM51">
         <v>-0.006444</v>
@@ -26367,7 +26379,7 @@
         <v>-0.956613</v>
       </c>
       <c r="AT51">
-        <v>-6.376899</v>
+        <v>-6.337738</v>
       </c>
     </row>
     <row r="52" spans="1:46">
@@ -26402,7 +26414,7 @@
         <v>391</v>
       </c>
       <c r="K52" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L52">
         <v>113</v>
@@ -26459,7 +26471,7 @@
         <v>-6.25866667</v>
       </c>
       <c r="AD52" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE52">
         <v>0.041111</v>
@@ -26483,7 +26495,7 @@
         <v>0.03609</v>
       </c>
       <c r="AL52">
-        <v>-20.757441</v>
+        <v>-20.601214</v>
       </c>
       <c r="AM52">
         <v>0.012533</v>
@@ -26507,7 +26519,7 @@
         <v>0.036222</v>
       </c>
       <c r="AT52">
-        <v>-6.326867</v>
+        <v>-6.279246</v>
       </c>
     </row>
     <row r="53" spans="1:46">
@@ -26542,7 +26554,7 @@
         <v>392</v>
       </c>
       <c r="K53" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L53">
         <v>122</v>
@@ -26599,7 +26611,7 @@
         <v>-6.37</v>
       </c>
       <c r="AD53" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE53">
         <v>-0.012222</v>
@@ -26623,7 +26635,7 @@
         <v>-0.810144</v>
       </c>
       <c r="AL53">
-        <v>-20.60279</v>
+        <v>-20.428176</v>
       </c>
       <c r="AM53">
         <v>-0.003711</v>
@@ -26647,7 +26659,7 @@
         <v>-0.809317</v>
       </c>
       <c r="AT53">
-        <v>-6.279731</v>
+        <v>-6.226507</v>
       </c>
     </row>
     <row r="54" spans="1:46">
@@ -26682,7 +26694,7 @@
         <v>393</v>
       </c>
       <c r="K54" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L54">
         <v>128</v>
@@ -26739,7 +26751,7 @@
         <v>-6.269</v>
       </c>
       <c r="AD54" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE54">
         <v>0.011111</v>
@@ -26763,7 +26775,7 @@
         <v>-0.427903</v>
       </c>
       <c r="AL54">
-        <v>-20.461428</v>
+        <v>-20.280308</v>
       </c>
       <c r="AM54">
         <v>0.003367</v>
@@ -26787,7 +26799,7 @@
         <v>-0.428915</v>
       </c>
       <c r="AT54">
-        <v>-6.236643</v>
+        <v>-6.181435</v>
       </c>
     </row>
     <row r="55" spans="1:46">
@@ -26822,7 +26834,7 @@
         <v>394</v>
       </c>
       <c r="K55" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L55">
         <v>129</v>
@@ -26879,7 +26891,7 @@
         <v>-6.08566667</v>
       </c>
       <c r="AD55" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE55">
         <v>0.02</v>
@@ -26903,7 +26915,7 @@
         <v>-0.280121</v>
       </c>
       <c r="AL55">
-        <v>-20.332604</v>
+        <v>-20.157327</v>
       </c>
       <c r="AM55">
         <v>0.006111</v>
@@ -26927,7 +26939,7 @@
         <v>-0.279277</v>
       </c>
       <c r="AT55">
-        <v>-6.197378</v>
+        <v>-6.143952</v>
       </c>
     </row>
     <row r="56" spans="1:46">
@@ -26962,7 +26974,7 @@
         <v>395</v>
       </c>
       <c r="K56" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L56">
         <v>134</v>
@@ -27019,7 +27031,7 @@
         <v>-6.12666667</v>
       </c>
       <c r="AD56" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE56">
         <v>-0.004444</v>
@@ -27043,7 +27055,7 @@
         <v>-0.67306</v>
       </c>
       <c r="AL56">
-        <v>-20.208862</v>
+        <v>-20.051985</v>
       </c>
       <c r="AM56">
         <v>-0.001367</v>
@@ -27067,7 +27079,7 @@
         <v>-0.673664</v>
       </c>
       <c r="AT56">
-        <v>-6.159661</v>
+        <v>-6.111844</v>
       </c>
     </row>
     <row r="57" spans="1:46">
@@ -27102,7 +27114,7 @@
         <v>396</v>
       </c>
       <c r="K57" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L57">
         <v>131</v>
@@ -27159,7 +27171,7 @@
         <v>-5.87233333</v>
       </c>
       <c r="AD57" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE57">
         <v>0.027778</v>
@@ -27183,7 +27195,7 @@
         <v>-0.138976</v>
       </c>
       <c r="AL57">
-        <v>-20.093014</v>
+        <v>-19.965188</v>
       </c>
       <c r="AM57">
         <v>0.008477999999999999</v>
@@ -27207,7 +27219,7 @@
         <v>-0.138337</v>
       </c>
       <c r="AT57">
-        <v>-6.124351</v>
+        <v>-6.085389</v>
       </c>
     </row>
     <row r="58" spans="1:46">
@@ -27242,7 +27254,7 @@
         <v>397</v>
       </c>
       <c r="K58" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L58">
         <v>126</v>
@@ -27299,7 +27311,7 @@
         <v>-6.00466667</v>
       </c>
       <c r="AD58" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE58">
         <v>-0.014444</v>
@@ -27323,7 +27335,7 @@
         <v>-0.830773</v>
       </c>
       <c r="AL58">
-        <v>-19.973887</v>
+        <v>-19.886114</v>
       </c>
       <c r="AM58">
         <v>-0.004411</v>
@@ -27347,7 +27359,7 @@
         <v>-0.831147</v>
       </c>
       <c r="AT58">
-        <v>-6.088041</v>
+        <v>-6.061288</v>
       </c>
     </row>
     <row r="59" spans="1:46">
@@ -27382,7 +27394,7 @@
         <v>398</v>
       </c>
       <c r="K59" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L59">
         <v>126</v>
@@ -27439,7 +27451,7 @@
         <v>-6.08566667</v>
       </c>
       <c r="AD59" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE59">
         <v>-0.008888999999999999</v>
@@ -27463,7 +27475,7 @@
         <v>-0.727916</v>
       </c>
       <c r="AL59">
-        <v>-19.84828</v>
+        <v>-19.809671</v>
       </c>
       <c r="AM59">
         <v>-0.0027</v>
@@ -27487,7 +27499,7 @@
         <v>-0.727303</v>
       </c>
       <c r="AT59">
-        <v>-6.049757</v>
+        <v>-6.037989</v>
       </c>
     </row>
     <row r="60" spans="1:46">
@@ -27522,7 +27534,7 @@
         <v>399</v>
       </c>
       <c r="K60" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L60">
         <v>130</v>
@@ -27579,7 +27591,7 @@
         <v>-6.06566667</v>
       </c>
       <c r="AD60" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE60">
         <v>0.002222</v>
@@ -27603,7 +27615,7 @@
         <v>-0.535231</v>
       </c>
       <c r="AL60">
-        <v>-19.713477</v>
+        <v>-19.729464</v>
       </c>
       <c r="AM60">
         <v>0.0006669999999999999</v>
@@ -27627,7 +27639,7 @@
         <v>-0.535752</v>
       </c>
       <c r="AT60">
-        <v>-6.008667</v>
+        <v>-6.013542</v>
       </c>
     </row>
     <row r="61" spans="1:46">
@@ -27662,7 +27674,7 @@
         <v>400</v>
       </c>
       <c r="K61" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L61">
         <v>125</v>
@@ -27719,7 +27731,7 @@
         <v>-6.06533333</v>
       </c>
       <c r="AD61" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -27743,7 +27755,7 @@
         <v>-0.566404</v>
       </c>
       <c r="AL61">
-        <v>-19.563965</v>
+        <v>-19.636383</v>
       </c>
       <c r="AM61">
         <v>1.1E-05</v>
@@ -27767,7 +27779,7 @@
         <v>-0.565761</v>
       </c>
       <c r="AT61">
-        <v>-5.963097</v>
+        <v>-5.985172</v>
       </c>
     </row>
     <row r="62" spans="1:46">
@@ -27802,7 +27814,7 @@
         <v>401</v>
       </c>
       <c r="K62" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L62">
         <v>124</v>
@@ -27859,7 +27871,7 @@
         <v>-6.025</v>
       </c>
       <c r="AD62" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE62">
         <v>0.004444</v>
@@ -27883,7 +27895,7 @@
         <v>-0.485782</v>
       </c>
       <c r="AL62">
-        <v>-19.395735</v>
+        <v>-19.521734</v>
       </c>
       <c r="AM62">
         <v>0.001344</v>
@@ -27907,7 +27919,7 @@
         <v>-0.486324</v>
       </c>
       <c r="AT62">
-        <v>-5.911818</v>
+        <v>-5.950226</v>
       </c>
     </row>
     <row r="63" spans="1:46">
@@ -27942,7 +27954,7 @@
         <v>402</v>
       </c>
       <c r="K63" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L63">
         <v>122</v>
@@ -27999,7 +28011,7 @@
         <v>-5.93333333</v>
       </c>
       <c r="AD63" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE63">
         <v>0.01</v>
@@ -28023,7 +28035,7 @@
         <v>-0.387009</v>
       </c>
       <c r="AL63">
-        <v>-19.206052</v>
+        <v>-19.377932</v>
       </c>
       <c r="AM63">
         <v>0.003056</v>
@@ -28047,7 +28059,7 @@
         <v>-0.386504</v>
       </c>
       <c r="AT63">
-        <v>-5.854003</v>
+        <v>-5.906395</v>
       </c>
     </row>
     <row r="64" spans="1:46">
@@ -28082,7 +28094,7 @@
         <v>403</v>
       </c>
       <c r="K64" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L64">
         <v>136</v>
@@ -28139,7 +28151,7 @@
         <v>-6.13666667</v>
       </c>
       <c r="AD64" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE64">
         <v>-0.022222</v>
@@ -28163,7 +28175,7 @@
         <v>-0.928369</v>
       </c>
       <c r="AL64">
-        <v>-18.980391</v>
+        <v>-19.187816</v>
       </c>
       <c r="AM64">
         <v>-0.006778</v>
@@ -28187,7 +28199,7 @@
         <v>-0.928596</v>
       </c>
       <c r="AT64">
-        <v>-5.78522</v>
+        <v>-5.848447</v>
       </c>
     </row>
     <row r="65" spans="1:46">
@@ -28222,7 +28234,7 @@
         <v>404</v>
       </c>
       <c r="K65" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L65">
         <v>128</v>
@@ -28279,7 +28291,7 @@
         <v>-6.16733333</v>
       </c>
       <c r="AD65" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE65">
         <v>-0.003333</v>
@@ -28303,7 +28315,7 @@
         <v>-0.595871</v>
       </c>
       <c r="AL65">
-        <v>-18.719966</v>
+        <v>-18.946423</v>
       </c>
       <c r="AM65">
         <v>-0.001022</v>
@@ -28327,7 +28339,7 @@
         <v>-0.596164</v>
       </c>
       <c r="AT65">
-        <v>-5.705839</v>
+        <v>-5.774866</v>
       </c>
     </row>
     <row r="66" spans="1:46">
@@ -28362,7 +28374,7 @@
         <v>405</v>
       </c>
       <c r="K66" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L66">
         <v>136</v>
@@ -28419,7 +28431,7 @@
         <v>-6.20766667</v>
       </c>
       <c r="AD66" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE66">
         <v>-0.004444</v>
@@ -28443,7 +28455,7 @@
         <v>-0.608576</v>
       </c>
       <c r="AL66">
-        <v>-18.421973</v>
+        <v>-18.646977</v>
       </c>
       <c r="AM66">
         <v>-0.001344</v>
@@ -28467,7 +28479,7 @@
         <v>-0.607917</v>
       </c>
       <c r="AT66">
-        <v>-5.615011</v>
+        <v>-5.683595</v>
       </c>
     </row>
     <row r="67" spans="1:46">
@@ -28502,7 +28514,7 @@
         <v>406</v>
       </c>
       <c r="K67" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L67">
         <v>130</v>
@@ -28559,7 +28571,7 @@
         <v>-1.31146914</v>
       </c>
       <c r="AD67" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE67">
         <v>0.003966</v>
@@ -28583,7 +28595,7 @@
         <v>-0.457643</v>
       </c>
       <c r="AL67">
-        <v>-18.148302</v>
+        <v>-18.354766</v>
       </c>
       <c r="AM67">
         <v>0.001209</v>
@@ -28607,7 +28619,7 @@
         <v>-0.457607</v>
       </c>
       <c r="AT67">
-        <v>-5.531595</v>
+        <v>-5.594527</v>
       </c>
     </row>
     <row r="68" spans="1:46">
@@ -28642,7 +28654,7 @@
         <v>407</v>
       </c>
       <c r="K68" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L68">
         <v>132</v>
@@ -28699,7 +28711,7 @@
         <v>-6.035</v>
       </c>
       <c r="AD68" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE68">
         <v>-0.516576</v>
@@ -28723,7 +28735,7 @@
         <v>-6.1249</v>
       </c>
       <c r="AL68">
-        <v>-18.098342</v>
+        <v>-18.299934</v>
       </c>
       <c r="AM68">
         <v>-0.157451</v>
@@ -28747,7 +28759,7 @@
         <v>-6.124631</v>
       </c>
       <c r="AT68">
-        <v>-5.516368</v>
+        <v>-5.577815</v>
       </c>
     </row>
     <row r="69" spans="1:46">
@@ -28782,7 +28794,7 @@
         <v>408</v>
       </c>
       <c r="K69" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L69">
         <v>139</v>
@@ -28839,7 +28851,7 @@
         <v>-5.76066667</v>
       </c>
       <c r="AD69" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE69">
         <v>0.03</v>
@@ -28863,7 +28875,7 @@
         <v>0.092983</v>
       </c>
       <c r="AL69">
-        <v>-17.761231</v>
+        <v>-17.919981</v>
       </c>
       <c r="AM69">
         <v>0.009143999999999999</v>
@@ -28887,7 +28899,7 @@
         <v>0.092971</v>
       </c>
       <c r="AT69">
-        <v>-5.413618</v>
+        <v>-5.462006</v>
       </c>
     </row>
     <row r="70" spans="1:46">
@@ -28922,7 +28934,7 @@
         <v>409</v>
       </c>
       <c r="K70" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L70">
         <v>134</v>
@@ -28979,7 +28991,7 @@
         <v>-5.73533333</v>
       </c>
       <c r="AD70" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE70">
         <v>0.001389</v>
@@ -29003,7 +29015,7 @@
         <v>-0.233196</v>
       </c>
       <c r="AL70">
-        <v>-17.462291</v>
+        <v>-17.571067</v>
       </c>
       <c r="AM70">
         <v>0.000422</v>
@@ -29027,7 +29039,7 @@
         <v>-0.233249</v>
       </c>
       <c r="AT70">
-        <v>-5.322498</v>
+        <v>-5.355652</v>
       </c>
     </row>
     <row r="71" spans="1:46">
@@ -29062,7 +29074,7 @@
         <v>410</v>
       </c>
       <c r="K71" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L71">
         <v>133</v>
@@ -29119,7 +29131,7 @@
         <v>-5.54733333</v>
       </c>
       <c r="AD71" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE71">
         <v>0.020556</v>
@@ -29143,7 +29155,7 @@
         <v>-0.011829</v>
       </c>
       <c r="AL71">
-        <v>-17.415822</v>
+        <v>-17.51601</v>
       </c>
       <c r="AM71">
         <v>0.006267</v>
@@ -29167,7 +29179,7 @@
         <v>-0.011753</v>
       </c>
       <c r="AT71">
-        <v>-5.308338</v>
+        <v>-5.338875</v>
       </c>
     </row>
     <row r="72" spans="1:46">
@@ -29202,7 +29214,7 @@
         <v>411</v>
       </c>
       <c r="K72" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L72">
         <v>122</v>
@@ -29259,7 +29271,7 @@
         <v>-5.466</v>
       </c>
       <c r="AD72" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE72">
         <v>0.008888999999999999</v>
@@ -29283,7 +29295,7 @@
         <v>-0.146457</v>
       </c>
       <c r="AL72">
-        <v>-17.062923</v>
+        <v>-17.092235</v>
       </c>
       <c r="AM72">
         <v>0.002711</v>
@@ -29307,7 +29319,7 @@
         <v>-0.146393</v>
       </c>
       <c r="AT72">
-        <v>-5.200776</v>
+        <v>-5.20971</v>
       </c>
     </row>
     <row r="73" spans="1:46">
@@ -29342,7 +29354,7 @@
         <v>412</v>
       </c>
       <c r="K73" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L73">
         <v>130</v>
@@ -29399,7 +29411,7 @@
         <v>-5.41516667</v>
       </c>
       <c r="AD73" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE73">
         <v>0.002778</v>
@@ -29423,7 +29435,7 @@
         <v>-0.216457</v>
       </c>
       <c r="AL73">
-        <v>-16.761197</v>
+        <v>-16.724122</v>
       </c>
       <c r="AM73">
         <v>0.000847</v>
@@ -29447,7 +29459,7 @@
         <v>-0.216431</v>
       </c>
       <c r="AT73">
-        <v>-5.108811</v>
+        <v>-5.097508</v>
       </c>
     </row>
     <row r="74" spans="1:46">
@@ -29482,7 +29494,7 @@
         <v>413</v>
       </c>
       <c r="K74" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L74">
         <v>132</v>
@@ -29539,7 +29551,7 @@
         <v>-5.36466667</v>
       </c>
       <c r="AD74" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE74">
         <v>0.005556</v>
@@ -29563,7 +29575,7 @@
         <v>-0.182387</v>
       </c>
       <c r="AL74">
-        <v>-16.713828</v>
+        <v>-16.666034</v>
       </c>
       <c r="AM74">
         <v>0.001683</v>
@@ -29587,7 +29599,7 @@
         <v>-0.182778</v>
       </c>
       <c r="AT74">
-        <v>-5.09437</v>
+        <v>-5.079799</v>
       </c>
     </row>
     <row r="75" spans="1:46">
@@ -29622,7 +29634,7 @@
         <v>414</v>
       </c>
       <c r="K75" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L75">
         <v>130</v>
@@ -29679,7 +29691,7 @@
         <v>-5.50666667</v>
       </c>
       <c r="AD75" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE75">
         <v>-0.015556</v>
@@ -29703,7 +29715,7 @@
         <v>-0.429624</v>
       </c>
       <c r="AL75">
-        <v>-16.364535</v>
+        <v>-16.237102</v>
       </c>
       <c r="AM75">
         <v>-0.004733</v>
@@ -29727,7 +29739,7 @@
         <v>-0.429288</v>
       </c>
       <c r="AT75">
-        <v>-4.987908</v>
+        <v>-4.949062</v>
       </c>
     </row>
     <row r="76" spans="1:46">
@@ -29762,7 +29774,7 @@
         <v>415</v>
       </c>
       <c r="K76" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L76">
         <v>142</v>
@@ -29819,7 +29831,7 @@
         <v>-5.43566667</v>
       </c>
       <c r="AD76" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE76">
         <v>0.003889</v>
@@ -29843,7 +29855,7 @@
         <v>-0.195999</v>
       </c>
       <c r="AL76">
-        <v>-16.087974</v>
+        <v>-15.899884</v>
       </c>
       <c r="AM76">
         <v>0.001183</v>
@@ -29867,7 +29879,7 @@
         <v>-0.196087</v>
       </c>
       <c r="AT76">
-        <v>-4.903613</v>
+        <v>-4.846279</v>
       </c>
     </row>
     <row r="77" spans="1:46">
@@ -29902,7 +29914,7 @@
         <v>416</v>
       </c>
       <c r="K77" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L77">
         <v>140</v>
@@ -29959,7 +29971,7 @@
         <v>-5.31366667</v>
       </c>
       <c r="AD77" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE77">
         <v>0.013333</v>
@@ -29983,7 +29995,7 @@
         <v>-0.081904</v>
       </c>
       <c r="AL77">
-        <v>-16.04926</v>
+        <v>-15.853152</v>
       </c>
       <c r="AM77">
         <v>0.004067</v>
@@ -30007,7 +30019,7 @@
         <v>-0.081771</v>
       </c>
       <c r="AT77">
-        <v>-4.891814</v>
+        <v>-4.832036</v>
       </c>
     </row>
     <row r="78" spans="1:46">
@@ -30042,7 +30054,7 @@
         <v>417</v>
       </c>
       <c r="K78" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L78">
         <v>141</v>
@@ -30099,7 +30111,7 @@
         <v>-4.97833333</v>
       </c>
       <c r="AD78" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE78">
         <v>0.036667</v>
@@ -30123,7 +30135,7 @@
         <v>0.199198</v>
       </c>
       <c r="AL78">
-        <v>-15.785529</v>
+        <v>-15.540998</v>
       </c>
       <c r="AM78">
         <v>0.011178</v>
@@ -30147,7 +30159,7 @@
         <v>0.199257</v>
       </c>
       <c r="AT78">
-        <v>-4.811432</v>
+        <v>-4.736895</v>
       </c>
     </row>
     <row r="79" spans="1:46">
@@ -30182,7 +30194,7 @@
         <v>418</v>
       </c>
       <c r="K79" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L79">
         <v>144</v>
@@ -30239,7 +30251,7 @@
         <v>-4.8565</v>
       </c>
       <c r="AD79" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE79">
         <v>0.006667</v>
@@ -30263,7 +30275,7 @@
         <v>-0.165195</v>
       </c>
       <c r="AL79">
-        <v>-15.601313</v>
+        <v>-15.334681</v>
       </c>
       <c r="AM79">
         <v>0.002031</v>
@@ -30287,7 +30299,7 @@
         <v>-0.165259</v>
       </c>
       <c r="AT79">
-        <v>-4.755282</v>
+        <v>-4.674009</v>
       </c>
     </row>
     <row r="80" spans="1:46">
@@ -30322,7 +30334,7 @@
         <v>419</v>
       </c>
       <c r="K80" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L80">
         <v>144</v>
@@ -30379,7 +30391,7 @@
         <v>-4.71433333</v>
       </c>
       <c r="AD80" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE80">
         <v>0.015556</v>
@@ -30403,7 +30415,7 @@
         <v>-0.055849</v>
       </c>
       <c r="AL80">
-        <v>-15.574326</v>
+        <v>-15.305907</v>
       </c>
       <c r="AM80">
         <v>0.004739</v>
@@ -30427,7 +30439,7 @@
         <v>-0.05596</v>
       </c>
       <c r="AT80">
-        <v>-4.747058</v>
+        <v>-4.66524</v>
       </c>
     </row>
     <row r="81" spans="1:46">
@@ -30462,7 +30474,7 @@
         <v>420</v>
       </c>
       <c r="K81" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L81">
         <v>146</v>
@@ -30519,7 +30531,7 @@
         <v>-4.55166667</v>
       </c>
       <c r="AD81" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE81">
         <v>0.017778</v>
@@ -30543,7 +30555,7 @@
         <v>-0.028236</v>
       </c>
       <c r="AL81">
-        <v>-15.41403</v>
+        <v>-15.149431</v>
       </c>
       <c r="AM81">
         <v>0.005422</v>
@@ -30567,7 +30579,7 @@
         <v>-0.02812</v>
       </c>
       <c r="AT81">
-        <v>-4.698201</v>
+        <v>-4.617549</v>
       </c>
     </row>
     <row r="82" spans="1:46">
@@ -30602,7 +30614,7 @@
         <v>421</v>
       </c>
       <c r="K82" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L82">
         <v>142</v>
@@ -30659,7 +30671,7 @@
         <v>-4.37383333</v>
       </c>
       <c r="AD82" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE82">
         <v>0.009722</v>
@@ -30683,7 +30695,7 @@
         <v>-0.127502</v>
       </c>
       <c r="AL82">
-        <v>-15.322816</v>
+        <v>-15.08292</v>
       </c>
       <c r="AM82">
         <v>0.002964</v>
@@ -30707,7 +30719,7 @@
         <v>-0.127461</v>
       </c>
       <c r="AT82">
-        <v>-4.670401</v>
+        <v>-4.597279</v>
       </c>
     </row>
     <row r="83" spans="1:46">
@@ -30742,7 +30754,7 @@
         <v>422</v>
       </c>
       <c r="K83" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L83">
         <v>150</v>
@@ -30799,7 +30811,7 @@
         <v>-4.10466667</v>
       </c>
       <c r="AD83" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE83">
         <v>0.029444</v>
@@ -30823,7 +30835,7 @@
         <v>0.118283</v>
       </c>
       <c r="AL83">
-        <v>-15.310987</v>
+        <v>-15.076997</v>
       </c>
       <c r="AM83">
         <v>0.008972000000000001</v>
@@ -30847,7 +30859,7 @@
         <v>0.118181</v>
       </c>
       <c r="AT83">
-        <v>-4.666796</v>
+        <v>-4.595474</v>
       </c>
     </row>
     <row r="84" spans="1:46">
@@ -30882,7 +30894,7 @@
         <v>423</v>
       </c>
       <c r="K84" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L84">
         <v>141</v>
@@ -30939,7 +30951,7 @@
         <v>-4.27733333</v>
       </c>
       <c r="AD84" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE84">
         <v>-0.018889</v>
@@ -30963,7 +30975,7 @@
         <v>-0.485966</v>
       </c>
       <c r="AL84">
-        <v>-15.253446</v>
+        <v>-15.071663</v>
       </c>
       <c r="AM84">
         <v>-0.005756</v>
@@ -30987,7 +30999,7 @@
         <v>-0.485924</v>
       </c>
       <c r="AT84">
-        <v>-4.649259</v>
+        <v>-4.593851</v>
       </c>
     </row>
     <row r="85" spans="1:46">
@@ -31022,7 +31034,7 @@
         <v>424</v>
       </c>
       <c r="K85" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L85">
         <v>149</v>
@@ -31079,7 +31091,7 @@
         <v>-4.22666667</v>
       </c>
       <c r="AD85" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE85">
         <v>0.005556</v>
@@ -31103,7 +31115,7 @@
         <v>-0.175947</v>
       </c>
       <c r="AL85">
-        <v>-15.248079</v>
+        <v>-15.075511</v>
       </c>
       <c r="AM85">
         <v>0.001689</v>
@@ -31127,7 +31139,7 @@
         <v>-0.176134</v>
       </c>
       <c r="AT85">
-        <v>-4.647623</v>
+        <v>-4.595025</v>
       </c>
     </row>
     <row r="86" spans="1:46">
@@ -31162,7 +31174,7 @@
         <v>425</v>
       </c>
       <c r="K86" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L86">
         <v>152</v>
@@ -31219,7 +31231,7 @@
         <v>-4.247</v>
       </c>
       <c r="AD86" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE86">
         <v>-0.002222</v>
@@ -31243,7 +31255,7 @@
         <v>-0.273089</v>
       </c>
       <c r="AL86">
-        <v>-15.227833</v>
+        <v>-15.135411</v>
       </c>
       <c r="AM86">
         <v>-0.000678</v>
@@ -31267,7 +31279,7 @@
         <v>-0.273131</v>
       </c>
       <c r="AT86">
-        <v>-4.641453</v>
+        <v>-4.613286</v>
       </c>
     </row>
     <row r="87" spans="1:46">
@@ -31302,7 +31314,7 @@
         <v>426</v>
       </c>
       <c r="K87" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L87">
         <v>148</v>
@@ -31359,7 +31371,7 @@
         <v>-4.33833333</v>
       </c>
       <c r="AD87" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE87">
         <v>-0.01</v>
@@ -31383,7 +31395,7 @@
         <v>-0.370048</v>
       </c>
       <c r="AL87">
-        <v>-15.227418</v>
+        <v>-15.150357</v>
       </c>
       <c r="AM87">
         <v>-0.003044</v>
@@ -31407,7 +31419,7 @@
         <v>-0.369872</v>
       </c>
       <c r="AT87">
-        <v>-4.641327</v>
+        <v>-4.617843</v>
       </c>
     </row>
     <row r="88" spans="1:46">
@@ -31442,7 +31454,7 @@
         <v>427</v>
       </c>
       <c r="K88" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L88">
         <v>182</v>
@@ -31499,7 +31511,7 @@
         <v>-4.6735</v>
       </c>
       <c r="AD88" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE88">
         <v>-0.018333</v>
@@ -31523,7 +31535,7 @@
         <v>-0.473742</v>
       </c>
       <c r="AL88">
-        <v>-15.283722</v>
+        <v>-15.484274</v>
       </c>
       <c r="AM88">
         <v>-0.005586</v>
@@ -31547,7 +31559,7 @@
         <v>-0.473678</v>
       </c>
       <c r="AT88">
-        <v>-4.65849</v>
+        <v>-4.719625</v>
       </c>
     </row>
     <row r="89" spans="1:46">
@@ -31582,7 +31594,7 @@
         <v>428</v>
       </c>
       <c r="K89" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L89">
         <v>180</v>
@@ -31639,7 +31651,7 @@
         <v>-4.75483333</v>
       </c>
       <c r="AD89" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE89">
         <v>-0.004444</v>
@@ -31663,7 +31675,7 @@
         <v>-0.292619</v>
       </c>
       <c r="AL89">
-        <v>-15.291308</v>
+        <v>-15.52001</v>
       </c>
       <c r="AM89">
         <v>-0.001356</v>
@@ -31687,7 +31699,7 @@
         <v>-0.292697</v>
       </c>
       <c r="AT89">
-        <v>-4.660803</v>
+        <v>-4.73052</v>
       </c>
     </row>
     <row r="90" spans="1:46">
@@ -31722,7 +31734,7 @@
         <v>429</v>
       </c>
       <c r="K90" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L90">
         <v>170</v>
@@ -31779,7 +31791,7 @@
         <v>-5.19166667</v>
       </c>
       <c r="AD90" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE90">
         <v>-0.047778</v>
@@ -31803,7 +31815,7 @@
         <v>-0.846684</v>
       </c>
       <c r="AL90">
-        <v>-15.325636</v>
+        <v>-15.743305</v>
       </c>
       <c r="AM90">
         <v>-0.014561</v>
@@ -31827,7 +31839,7 @@
         <v>-0.846554</v>
       </c>
       <c r="AT90">
-        <v>-4.671267</v>
+        <v>-4.798582</v>
       </c>
     </row>
     <row r="91" spans="1:46">
@@ -31862,7 +31874,7 @@
         <v>430</v>
       </c>
       <c r="K91" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L91">
         <v>177</v>
@@ -31919,7 +31931,7 @@
         <v>-5.09016667</v>
       </c>
       <c r="AD91" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE91">
         <v>0.005556</v>
@@ -31943,7 +31955,7 @@
         <v>-0.152488</v>
       </c>
       <c r="AL91">
-        <v>-15.294673</v>
+        <v>-15.84321</v>
       </c>
       <c r="AM91">
         <v>0.001692</v>
@@ -31967,7 +31979,7 @@
         <v>-0.15255</v>
       </c>
       <c r="AT91">
-        <v>-4.661831</v>
+        <v>-4.829034</v>
       </c>
     </row>
     <row r="92" spans="1:46">
@@ -32002,7 +32014,7 @@
         <v>431</v>
       </c>
       <c r="K92" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L92">
         <v>166</v>
@@ -32059,7 +32071,7 @@
         <v>-4.97833333</v>
       </c>
       <c r="AD92" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE92">
         <v>0.012222</v>
@@ -32083,7 +32095,7 @@
         <v>-0.064994</v>
       </c>
       <c r="AL92">
-        <v>-15.27899</v>
+        <v>-15.846313</v>
       </c>
       <c r="AM92">
         <v>0.003728</v>
@@ -32107,7 +32119,7 @@
         <v>-0.06486699999999999</v>
       </c>
       <c r="AT92">
-        <v>-4.657051</v>
+        <v>-4.82998</v>
       </c>
     </row>
     <row r="93" spans="1:46">
@@ -32142,7 +32154,7 @@
         <v>432</v>
       </c>
       <c r="K93" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L93">
         <v>180</v>
@@ -32199,7 +32211,7 @@
         <v>-5.36466667</v>
       </c>
       <c r="AD93" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE93">
         <v>-0.042222</v>
@@ -32223,7 +32235,7 @@
         <v>-0.773837</v>
       </c>
       <c r="AL93">
-        <v>-15.028853</v>
+        <v>-15.653805</v>
       </c>
       <c r="AM93">
         <v>-0.012878</v>
@@ -32247,7 +32259,7 @@
         <v>-0.774195</v>
       </c>
       <c r="AT93">
-        <v>-4.58081</v>
+        <v>-4.7713</v>
       </c>
     </row>
     <row r="94" spans="1:46">
@@ -32282,7 +32294,7 @@
         <v>433</v>
       </c>
       <c r="K94" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L94">
         <v>178</v>
@@ -32339,7 +32351,7 @@
         <v>-4.70416667</v>
       </c>
       <c r="AD94" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE94">
         <v>0.036111</v>
@@ -32363,7 +32375,7 @@
         <v>0.256721</v>
       </c>
       <c r="AL94">
-        <v>-14.703288</v>
+        <v>-15.266316</v>
       </c>
       <c r="AM94">
         <v>0.011008</v>
@@ -32387,7 +32399,7 @@
         <v>0.256778</v>
       </c>
       <c r="AT94">
-        <v>-4.481581</v>
+        <v>-4.653189</v>
       </c>
     </row>
     <row r="95" spans="1:46">
@@ -32422,7 +32434,7 @@
         <v>434</v>
       </c>
       <c r="K95" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L95">
         <v>156</v>
@@ -32479,7 +32491,7 @@
         <v>-3.69833333</v>
       </c>
       <c r="AD95" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE95">
         <v>0.11</v>
@@ -32503,7 +32515,7 @@
         <v>1.218598</v>
       </c>
       <c r="AL95">
-        <v>-14.649413</v>
+        <v>-15.197279</v>
       </c>
       <c r="AM95">
         <v>0.033528</v>
@@ -32527,7 +32539,7 @@
         <v>1.218544</v>
       </c>
       <c r="AT95">
-        <v>-4.465156</v>
+        <v>-4.63214</v>
       </c>
     </row>
     <row r="96" spans="1:46">
@@ -32562,7 +32574,7 @@
         <v>435</v>
       </c>
       <c r="K96" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L96">
         <v>142</v>
@@ -32619,7 +32631,7 @@
         <v>-3.26133333</v>
       </c>
       <c r="AD96" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE96">
         <v>0.047778</v>
@@ -32643,7 +32655,7 @@
         <v>0.39442</v>
       </c>
       <c r="AL96">
-        <v>-14.189325</v>
+        <v>-14.578997</v>
       </c>
       <c r="AM96">
         <v>0.014567</v>
@@ -32667,7 +32679,7 @@
         <v>0.394603</v>
       </c>
       <c r="AT96">
-        <v>-4.32493</v>
+        <v>-4.443689</v>
       </c>
     </row>
     <row r="97" spans="1:46">
@@ -32702,7 +32714,7 @@
         <v>436</v>
       </c>
       <c r="K97" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L97">
         <v>146</v>
@@ -32759,7 +32771,7 @@
         <v>-4.379</v>
       </c>
       <c r="AD97" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE97">
         <v>-0.122222</v>
@@ -32783,7 +32795,7 @@
         <v>-1.818079</v>
       </c>
       <c r="AL97">
-        <v>-13.089189</v>
+        <v>-12.998668</v>
       </c>
       <c r="AM97">
         <v>-0.037256</v>
@@ -32807,7 +32819,7 @@
         <v>-1.818092</v>
       </c>
       <c r="AT97">
-        <v>-3.989614</v>
+        <v>-3.961987</v>
       </c>
     </row>
     <row r="98" spans="1:46">
@@ -32842,7 +32854,7 @@
         <v>437</v>
       </c>
       <c r="K98" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L98">
         <v>156</v>
@@ -32899,7 +32911,7 @@
         <v>-4.003</v>
       </c>
       <c r="AD98" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AE98">
         <v>0.020556</v>
@@ -32923,7 +32935,7 @@
         <v>0.05191</v>
       </c>
       <c r="AL98">
-        <v>-12.830892</v>
+        <v>-12.616729</v>
       </c>
       <c r="AM98">
         <v>0.006267</v>
@@ -32947,7 +32959,287 @@
         <v>0.051972</v>
       </c>
       <c r="AT98">
-        <v>-3.910885</v>
+        <v>-3.845567</v>
+      </c>
+    </row>
+    <row r="99" spans="1:46">
+      <c r="A99" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" t="s">
+        <v>92</v>
+      </c>
+      <c r="C99" s="2">
+        <v>45969.38877582176</v>
+      </c>
+      <c r="D99" s="2">
+        <v>45969.38871527778</v>
+      </c>
+      <c r="E99">
+        <v>4606</v>
+      </c>
+      <c r="F99">
+        <v>1403.91</v>
+      </c>
+      <c r="G99">
+        <v>-968</v>
+      </c>
+      <c r="H99">
+        <v>2580</v>
+      </c>
+      <c r="I99" t="s">
+        <v>340</v>
+      </c>
+      <c r="J99" t="s">
+        <v>438</v>
+      </c>
+      <c r="K99" t="s">
+        <v>537</v>
+      </c>
+      <c r="L99">
+        <v>140</v>
+      </c>
+      <c r="M99">
+        <v>8</v>
+      </c>
+      <c r="N99">
+        <v>12.9</v>
+      </c>
+      <c r="O99">
+        <v>39.414</v>
+      </c>
+      <c r="P99">
+        <v>-102.4771666667</v>
+      </c>
+      <c r="Q99">
+        <v>101.61</v>
+      </c>
+      <c r="R99">
+        <v>163.53</v>
+      </c>
+      <c r="S99">
+        <v>40.28</v>
+      </c>
+      <c r="T99">
+        <v>4.6</v>
+      </c>
+      <c r="U99">
+        <v>277.75</v>
+      </c>
+      <c r="V99">
+        <v>86220</v>
+      </c>
+      <c r="W99">
+        <v>0.85</v>
+      </c>
+      <c r="X99">
+        <v>0.00209831</v>
+      </c>
+      <c r="Y99">
+        <v>1.08142499</v>
+      </c>
+      <c r="Z99">
+        <v>1.667E-05</v>
+      </c>
+      <c r="AA99">
+        <v>-3.889E-05</v>
+      </c>
+      <c r="AB99">
+        <v>-16.13333333</v>
+      </c>
+      <c r="AC99">
+        <v>-4.91733333</v>
+      </c>
+      <c r="AD99" t="s">
+        <v>539</v>
+      </c>
+      <c r="AE99">
+        <v>-0.1</v>
+      </c>
+      <c r="AF99">
+        <v>-28.094671</v>
+      </c>
+      <c r="AG99">
+        <v>0.015411</v>
+      </c>
+      <c r="AH99">
+        <v>17.216124</v>
+      </c>
+      <c r="AI99">
+        <v>0.07646500000000001</v>
+      </c>
+      <c r="AJ99">
+        <v>0.694775</v>
+      </c>
+      <c r="AK99">
+        <v>-1.509331</v>
+      </c>
+      <c r="AL99">
+        <v>-9.321662</v>
+      </c>
+      <c r="AM99">
+        <v>-0.030478</v>
+      </c>
+      <c r="AN99">
+        <v>-8.563257</v>
+      </c>
+      <c r="AO99">
+        <v>0.004697</v>
+      </c>
+      <c r="AP99">
+        <v>5.247478</v>
+      </c>
+      <c r="AQ99">
+        <v>0.023307</v>
+      </c>
+      <c r="AR99">
+        <v>0.6947950000000001</v>
+      </c>
+      <c r="AS99">
+        <v>-1.509203</v>
+      </c>
+      <c r="AT99">
+        <v>-2.841231</v>
+      </c>
+    </row>
+    <row r="100" spans="1:46">
+      <c r="A100" t="s">
+        <v>37</v>
+      </c>
+      <c r="B100" t="s">
+        <v>92</v>
+      </c>
+      <c r="C100" s="2">
+        <v>45969.39708081019</v>
+      </c>
+      <c r="D100" s="2">
+        <v>45969.39704861111</v>
+      </c>
+      <c r="E100">
+        <v>4206</v>
+      </c>
+      <c r="F100">
+        <v>1281.99</v>
+      </c>
+      <c r="G100">
+        <v>-33.3</v>
+      </c>
+      <c r="H100">
+        <v>3300</v>
+      </c>
+      <c r="I100" t="s">
+        <v>340</v>
+      </c>
+      <c r="J100" t="s">
+        <v>439</v>
+      </c>
+      <c r="K100" t="s">
+        <v>538</v>
+      </c>
+      <c r="L100">
+        <v>170</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>39.4126666667</v>
+      </c>
+      <c r="P100">
+        <v>-102.4765</v>
+      </c>
+      <c r="Q100">
+        <v>101.7</v>
+      </c>
+      <c r="R100">
+        <v>163.66</v>
+      </c>
+      <c r="S100">
+        <v>56.84</v>
+      </c>
+      <c r="T100">
+        <v>13.8</v>
+      </c>
+      <c r="U100">
+        <v>286.95</v>
+      </c>
+      <c r="V100">
+        <v>87620</v>
+      </c>
+      <c r="W100">
+        <v>0.86</v>
+      </c>
+      <c r="X100">
+        <v>0.00206402</v>
+      </c>
+      <c r="Y100">
+        <v>1.06374974</v>
+      </c>
+      <c r="Z100">
+        <v>9.3E-07</v>
+      </c>
+      <c r="AA100">
+        <v>-1.85E-06</v>
+      </c>
+      <c r="AB100">
+        <v>-0.5555555599999999</v>
+      </c>
+      <c r="AC100">
+        <v>-0.16933333</v>
+      </c>
+      <c r="AD100" t="s">
+        <v>539</v>
+      </c>
+      <c r="AE100">
+        <v>0.021636</v>
+      </c>
+      <c r="AF100">
+        <v>-27.816498</v>
+      </c>
+      <c r="AG100">
+        <v>0.015475</v>
+      </c>
+      <c r="AH100">
+        <v>17.350248</v>
+      </c>
+      <c r="AI100">
+        <v>0.076073</v>
+      </c>
+      <c r="AJ100">
+        <v>1.571213</v>
+      </c>
+      <c r="AK100">
+        <v>0.080988</v>
+      </c>
+      <c r="AL100">
+        <v>-5.124269</v>
+      </c>
+      <c r="AM100">
+        <v>0.006594</v>
+      </c>
+      <c r="AN100">
+        <v>-8.47847</v>
+      </c>
+      <c r="AO100">
+        <v>0.004717</v>
+      </c>
+      <c r="AP100">
+        <v>5.288359</v>
+      </c>
+      <c r="AQ100">
+        <v>0.023188</v>
+      </c>
+      <c r="AR100">
+        <v>1.571213</v>
+      </c>
+      <c r="AS100">
+        <v>0.08094700000000001</v>
+      </c>
+      <c r="AT100">
+        <v>-1.561847</v>
       </c>
     </row>
   </sheetData>

--- a/www/flightdata/xlsx/eoss-387.xlsx
+++ b/www/flightdata/xlsx/eoss-387.xlsx
@@ -2148,7 +2148,7 @@
         <v>27272.59</v>
       </c>
       <c r="I2">
-        <v>355</v>
+        <v>221</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>

--- a/www/flightdata/xlsx/eoss-387.xlsx
+++ b/www/flightdata/xlsx/eoss-387.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="553">
   <si>
     <t>flight</t>
   </si>
@@ -57,6 +57,21 @@
     <t>range_distance_traveled_km</t>
   </si>
   <si>
+    <t>parachute.description</t>
+  </si>
+  <si>
+    <t>parachute.size_ft</t>
+  </si>
+  <si>
+    <t>parachute.size_m</t>
+  </si>
+  <si>
+    <t>parachute.weight_lb</t>
+  </si>
+  <si>
+    <t>parachute.weight_kg</t>
+  </si>
+  <si>
     <t>weights.client_lb</t>
   </si>
   <si>
@@ -99,6 +114,15 @@
     <t>weights.necklift_kg</t>
   </si>
   <si>
+    <t>detected_burst.detected</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_ft</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_m</t>
+  </si>
+  <si>
     <t>launch_location.latitude</t>
   </si>
   <si>
@@ -148,6 +172,12 @@
   </si>
   <si>
     <t>1hrs 37mins 7secs</t>
+  </si>
+  <si>
+    <t>Rocketman</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>flightid</t>
@@ -2006,10 +2036,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2121,25 +2151,49 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>89477</v>
@@ -2151,7 +2205,7 @@
         <v>221</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>5827</v>
@@ -2162,76 +2216,100 @@
       <c r="M2">
         <v>163.59</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2">
+        <v>3.66</v>
+      </c>
+      <c r="Q2">
+        <v>1.7</v>
+      </c>
+      <c r="R2">
+        <v>0.77</v>
+      </c>
+      <c r="S2">
         <v>9.630000000000001</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>4.37</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>3.24</v>
       </c>
-      <c r="Q2">
+      <c r="V2">
         <v>1.47</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>1.7</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>0.77</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>14.57</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>6.61</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>6.61</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <v>3</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>21.19</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>9.609999999999999</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>18.81</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>8.529999999999999</v>
       </c>
-      <c r="AB2">
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>89811</v>
+      </c>
+      <c r="AI2">
+        <v>27374.39</v>
+      </c>
+      <c r="AJ2">
         <v>40.2248333333</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <v>-104.0771666667</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
         <v>4564</v>
       </c>
-      <c r="AE2">
+      <c r="AM2">
         <v>1391.11</v>
       </c>
-      <c r="AF2">
+      <c r="AN2">
         <v>39.414</v>
       </c>
-      <c r="AG2">
+      <c r="AO2">
         <v>-102.4771666667</v>
       </c>
-      <c r="AH2">
+      <c r="AP2">
         <v>101.65</v>
       </c>
-      <c r="AI2">
+      <c r="AQ2">
         <v>163.59</v>
       </c>
-      <c r="AJ2">
+      <c r="AR2">
         <v>4606</v>
       </c>
-      <c r="AK2">
+      <c r="AS2">
         <v>1403.91</v>
       </c>
     </row>
@@ -2247,156 +2325,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>45969.32130298611</v>
@@ -2417,16 +2495,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="M2">
         <v>211</v>
@@ -2483,7 +2561,7 @@
         <v>0.09166667000000001</v>
       </c>
       <c r="AE2" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AG2">
         <v>0.3</v>
@@ -2500,10 +2578,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>45969.32137578704</v>
@@ -2524,16 +2602,16 @@
         <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L3" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="M3">
         <v>356</v>
@@ -2590,7 +2668,7 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="AE3" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF3">
         <v>-0.002222</v>
@@ -2631,10 +2709,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>45969.32167913194</v>
@@ -2655,16 +2733,16 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="M4">
         <v>184</v>
@@ -2721,7 +2799,7 @@
         <v>0.92433333</v>
       </c>
       <c r="AE4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF4">
         <v>0.093333</v>
@@ -2774,10 +2852,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2">
         <v>45969.32172347223</v>
@@ -2798,16 +2876,16 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="M5">
         <v>173</v>
@@ -2864,7 +2942,7 @@
         <v>3.75933333</v>
       </c>
       <c r="AE5" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF5">
         <v>0.31</v>
@@ -2917,10 +2995,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>45969.32199767361</v>
@@ -2941,16 +3019,16 @@
         <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="M6">
         <v>162</v>
@@ -3007,7 +3085,7 @@
         <v>7.05133333</v>
       </c>
       <c r="AE6" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF6">
         <v>0.36</v>
@@ -3060,10 +3138,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2">
         <v>45969.32206953704</v>
@@ -3084,16 +3162,16 @@
         <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L7" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="M7">
         <v>154</v>
@@ -3150,7 +3228,7 @@
         <v>6.62433333</v>
       </c>
       <c r="AE7" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF7">
         <v>-0.046667</v>
@@ -3203,10 +3281,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>45969.32237331018</v>
@@ -3227,16 +3305,16 @@
         <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="M8">
         <v>159</v>
@@ -3293,7 +3371,7 @@
         <v>7.26433333</v>
       </c>
       <c r="AE8" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF8">
         <v>0.07000000000000001</v>
@@ -3346,10 +3424,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2">
         <v>45969.32241803241</v>
@@ -3370,16 +3448,16 @@
         <v>97</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L9" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="M9">
         <v>153</v>
@@ -3436,7 +3514,7 @@
         <v>7.305</v>
       </c>
       <c r="AE9" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF9">
         <v>0.004444</v>
@@ -3489,10 +3567,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>45969.32269164352</v>
@@ -3513,16 +3591,16 @@
         <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="M10">
         <v>146</v>
@@ -3579,7 +3657,7 @@
         <v>7.173</v>
       </c>
       <c r="AE10" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF10">
         <v>-0.014444</v>
@@ -3632,10 +3710,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>45969.32276412037</v>
@@ -3656,16 +3734,16 @@
         <v>127</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="M11">
         <v>146</v>
@@ -3722,7 +3800,7 @@
         <v>7.08166667</v>
       </c>
       <c r="AE11" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF11">
         <v>-0.01</v>
@@ -3775,10 +3853,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>45969.32306399306</v>
@@ -3799,16 +3877,16 @@
         <v>150</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L12" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="M12">
         <v>137</v>
@@ -3865,7 +3943,7 @@
         <v>6.604</v>
       </c>
       <c r="AE12" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF12">
         <v>-0.052222</v>
@@ -3918,10 +3996,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2">
         <v>45969.32310844908</v>
@@ -3942,16 +4020,16 @@
         <v>157</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="M13">
         <v>136</v>
@@ -4008,7 +4086,7 @@
         <v>6.65466667</v>
       </c>
       <c r="AE13" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF13">
         <v>0.005556</v>
@@ -4061,10 +4139,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>45969.32338238426</v>
@@ -4085,16 +4163,16 @@
         <v>180</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L14" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="M14">
         <v>134</v>
@@ -4151,7 +4229,7 @@
         <v>7.183</v>
       </c>
       <c r="AE14" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF14">
         <v>0.057778</v>
@@ -4204,10 +4282,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>45969.32345548611</v>
@@ -4228,16 +4306,16 @@
         <v>187</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="M15">
         <v>131</v>
@@ -4294,7 +4372,7 @@
         <v>7.14233333</v>
       </c>
       <c r="AE15" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF15">
         <v>-0.004444</v>
@@ -4347,10 +4425,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>45969.32375868056</v>
@@ -4371,16 +4449,16 @@
         <v>210</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L16" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="M16">
         <v>125</v>
@@ -4437,7 +4515,7 @@
         <v>7.01033333</v>
       </c>
       <c r="AE16" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF16">
         <v>-0.014444</v>
@@ -4490,10 +4568,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>45969.32407682871</v>
@@ -4514,16 +4592,16 @@
         <v>240</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L17" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="M17">
         <v>128</v>
@@ -4580,7 +4658,7 @@
         <v>7.31533333</v>
       </c>
       <c r="AE17" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF17">
         <v>0.033333</v>
@@ -4633,10 +4711,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2">
         <v>45969.32445314815</v>
@@ -4657,16 +4735,16 @@
         <v>270</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="M18">
         <v>109</v>
@@ -4723,7 +4801,7 @@
         <v>7.051</v>
       </c>
       <c r="AE18" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF18">
         <v>-0.028889</v>
@@ -4776,10 +4854,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2">
         <v>45969.3244974537</v>
@@ -4800,16 +4878,16 @@
         <v>277</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="M19">
         <v>120</v>
@@ -4866,7 +4944,7 @@
         <v>7.13911111</v>
       </c>
       <c r="AE19" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF19">
         <v>0.00321</v>
@@ -4919,10 +4997,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>45969.32477153935</v>
@@ -4943,16 +5021,16 @@
         <v>300</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="M20">
         <v>115</v>
@@ -5009,7 +5087,7 @@
         <v>7.02066667</v>
       </c>
       <c r="AE20" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF20">
         <v>-0.012963</v>
@@ -5062,10 +5140,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>45969.32514778935</v>
@@ -5086,16 +5164,16 @@
         <v>330</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L21" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M21">
         <v>122</v>
@@ -5152,7 +5230,7 @@
         <v>7.90433333</v>
       </c>
       <c r="AE21" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF21">
         <v>0.096667</v>
@@ -5205,10 +5283,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2">
         <v>45969.32519194444</v>
@@ -5229,16 +5307,16 @@
         <v>337</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L22" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M22">
         <v>127</v>
@@ -5295,7 +5373,7 @@
         <v>7.56933333</v>
       </c>
       <c r="AE22" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF22">
         <v>-0.018333</v>
@@ -5348,10 +5426,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2">
         <v>45969.32546936342</v>
@@ -5372,16 +5450,16 @@
         <v>360</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M23">
         <v>129</v>
@@ -5438,7 +5516,7 @@
         <v>7.38633333</v>
       </c>
       <c r="AE23" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF23">
         <v>-0.02</v>
@@ -5491,10 +5569,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2">
         <v>45969.32553862269</v>
@@ -5515,16 +5593,16 @@
         <v>367</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M24">
         <v>126</v>
@@ -5581,7 +5659,7 @@
         <v>7.14233333</v>
       </c>
       <c r="AE24" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF24">
         <v>-0.026667</v>
@@ -5634,10 +5712,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>45969.3258422338</v>
@@ -5658,16 +5736,16 @@
         <v>390</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M25">
         <v>114</v>
@@ -5724,7 +5802,7 @@
         <v>7.366</v>
       </c>
       <c r="AE25" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF25">
         <v>0.024444</v>
@@ -5777,10 +5855,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2">
         <v>45969.32588547454</v>
@@ -5801,16 +5879,16 @@
         <v>397</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M26">
         <v>115</v>
@@ -5867,7 +5945,7 @@
         <v>7.50833333</v>
       </c>
       <c r="AE26" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF26">
         <v>0.015556</v>
@@ -5920,10 +5998,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2">
         <v>45969.32616034722</v>
@@ -5944,16 +6022,16 @@
         <v>420</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M27">
         <v>127</v>
@@ -6010,7 +6088,7 @@
         <v>7.63</v>
       </c>
       <c r="AE27" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF27">
         <v>0.013333</v>
@@ -6063,10 +6141,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>45969.3262330787</v>
@@ -6087,16 +6165,16 @@
         <v>427</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M28">
         <v>112</v>
@@ -6153,7 +6231,7 @@
         <v>7.691</v>
       </c>
       <c r="AE28" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF28">
         <v>0.006667</v>
@@ -6206,10 +6284,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>45969.32654267361</v>
@@ -6230,16 +6308,16 @@
         <v>450</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="M29">
         <v>132</v>
@@ -6296,7 +6374,7 @@
         <v>7.57966667</v>
       </c>
       <c r="AE29" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF29">
         <v>-0.012222</v>
@@ -6349,10 +6427,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2">
         <v>45969.32685826389</v>
@@ -6373,16 +6451,16 @@
         <v>480</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M30">
         <v>141</v>
@@ -6439,7 +6517,7 @@
         <v>7.66033333</v>
       </c>
       <c r="AE30" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF30">
         <v>0.008888999999999999</v>
@@ -6492,10 +6570,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2">
         <v>45969.32723150463</v>
@@ -6516,16 +6594,16 @@
         <v>510</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="M31">
         <v>137</v>
@@ -6582,7 +6660,7 @@
         <v>7.62</v>
       </c>
       <c r="AE31" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF31">
         <v>-0.004444</v>
@@ -6635,10 +6713,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2">
         <v>45969.32727459491</v>
@@ -6659,16 +6737,16 @@
         <v>517</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M32">
         <v>126</v>
@@ -6725,7 +6803,7 @@
         <v>7.58955556</v>
       </c>
       <c r="AE32" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF32">
         <v>-0.001111</v>
@@ -6778,10 +6856,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>45969.32754943287</v>
@@ -6802,16 +6880,16 @@
         <v>540</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="M33">
         <v>130</v>
@@ -6868,7 +6946,7 @@
         <v>7.07166667</v>
       </c>
       <c r="AE33" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF33">
         <v>-0.056667</v>
@@ -6921,10 +6999,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2">
         <v>45969.32762224537</v>
@@ -6945,16 +7023,16 @@
         <v>547</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M34">
         <v>125</v>
@@ -7011,7 +7089,7 @@
         <v>6.81733333</v>
       </c>
       <c r="AE34" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF34">
         <v>-0.027778</v>
@@ -7064,10 +7142,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>45969.32792599537</v>
@@ -7088,16 +7166,16 @@
         <v>570</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M35">
         <v>125</v>
@@ -7154,7 +7232,7 @@
         <v>6.75633333</v>
       </c>
       <c r="AE35" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF35">
         <v>-0.006667</v>
@@ -7207,10 +7285,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>45969.32796908565</v>
@@ -7231,16 +7309,16 @@
         <v>577</v>
       </c>
       <c r="I36" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M36">
         <v>126</v>
@@ -7297,7 +7375,7 @@
         <v>6.736</v>
       </c>
       <c r="AE36" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF36">
         <v>-0.002222</v>
@@ -7350,10 +7428,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>45969.32824403935</v>
@@ -7374,16 +7452,16 @@
         <v>600</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M37">
         <v>123</v>
@@ -7440,7 +7518,7 @@
         <v>6.45166667</v>
       </c>
       <c r="AE37" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF37">
         <v>-0.031111</v>
@@ -7493,10 +7571,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>45969.32831622685</v>
@@ -7517,16 +7595,16 @@
         <v>607</v>
       </c>
       <c r="I38" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M38">
         <v>126</v>
@@ -7583,7 +7661,7 @@
         <v>6.52266667</v>
       </c>
       <c r="AE38" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF38">
         <v>0.007778</v>
@@ -7636,10 +7714,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2">
         <v>45969.32861988426</v>
@@ -7660,16 +7738,16 @@
         <v>630</v>
       </c>
       <c r="I39" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="M39">
         <v>119</v>
@@ -7726,7 +7804,7 @@
         <v>6.38033333</v>
       </c>
       <c r="AE39" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF39">
         <v>-0.015556</v>
@@ -7779,10 +7857,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>45969.32893873843</v>
@@ -7803,16 +7881,16 @@
         <v>660</v>
       </c>
       <c r="I40" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M40">
         <v>135</v>
@@ -7869,7 +7947,7 @@
         <v>6.56333333</v>
       </c>
       <c r="AE40" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF40">
         <v>0.02</v>
@@ -7922,10 +8000,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C41" s="2">
         <v>45969.32901064815</v>
@@ -7946,16 +8024,16 @@
         <v>667</v>
       </c>
       <c r="I41" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M41">
         <v>126</v>
@@ -8012,7 +8090,7 @@
         <v>6.38566667</v>
       </c>
       <c r="AE41" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF41">
         <v>-0.009722</v>
@@ -8065,10 +8143,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2">
         <v>45969.32931466436</v>
@@ -8089,16 +8167,16 @@
         <v>690</v>
       </c>
       <c r="I42" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="M42">
         <v>131</v>
@@ -8155,7 +8233,7 @@
         <v>6.56333333</v>
       </c>
       <c r="AE42" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF42">
         <v>0.019444</v>
@@ -8208,10 +8286,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C43" s="2">
         <v>45969.32935774305</v>
@@ -8232,16 +8310,16 @@
         <v>697</v>
       </c>
       <c r="I43" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L43" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M43">
         <v>122</v>
@@ -8298,7 +8376,7 @@
         <v>6.736</v>
       </c>
       <c r="AE43" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF43">
         <v>0.018889</v>
@@ -8351,10 +8429,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2">
         <v>45969.32963326389</v>
@@ -8375,16 +8453,16 @@
         <v>720</v>
       </c>
       <c r="I44" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M44">
         <v>121</v>
@@ -8441,7 +8519,7 @@
         <v>7.25433333</v>
       </c>
       <c r="AE44" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF44">
         <v>0.056667</v>
@@ -8494,10 +8572,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2">
         <v>45969.32970574074</v>
@@ -8518,16 +8596,16 @@
         <v>727</v>
       </c>
       <c r="I45" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L45" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M45">
         <v>125</v>
@@ -8584,7 +8662,7 @@
         <v>7.315</v>
       </c>
       <c r="AE45" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF45">
         <v>0.006667</v>
@@ -8637,10 +8715,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2">
         <v>45969.33001269676</v>
@@ -8661,16 +8739,16 @@
         <v>750</v>
       </c>
       <c r="I46" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="M46">
         <v>132</v>
@@ -8727,7 +8805,7 @@
         <v>7.72166667</v>
       </c>
       <c r="AE46" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF46">
         <v>0.044444</v>
@@ -8780,10 +8858,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2">
         <v>45969.33005300926</v>
@@ -8804,16 +8882,16 @@
         <v>757</v>
       </c>
       <c r="I47" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="M47">
         <v>122</v>
@@ -8870,7 +8948,7 @@
         <v>7.864</v>
       </c>
       <c r="AE47" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF47">
         <v>0.015556</v>
@@ -8923,10 +9001,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2">
         <v>45969.33032761574</v>
@@ -8947,16 +9025,16 @@
         <v>780</v>
       </c>
       <c r="I48" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L48" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M48">
         <v>117</v>
@@ -9013,7 +9091,7 @@
         <v>8.229333329999999</v>
       </c>
       <c r="AE48" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF48">
         <v>0.04</v>
@@ -9066,10 +9144,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C49" s="2">
         <v>45969.33039966435</v>
@@ -9090,16 +9168,16 @@
         <v>787</v>
       </c>
       <c r="I49" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L49" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M49">
         <v>117</v>
@@ -9156,7 +9234,7 @@
         <v>8.25</v>
       </c>
       <c r="AE49" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF49">
         <v>0.002222</v>
@@ -9209,10 +9287,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2">
         <v>45969.33070375</v>
@@ -9233,16 +9311,16 @@
         <v>810</v>
       </c>
       <c r="I50" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="L50" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M50">
         <v>118</v>
@@ -9299,7 +9377,7 @@
         <v>8.35166667</v>
       </c>
       <c r="AE50" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF50">
         <v>0.011111</v>
@@ -9352,10 +9430,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2">
         <v>45969.33074724537</v>
@@ -9376,16 +9454,16 @@
         <v>817</v>
       </c>
       <c r="I51" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="L51" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="M51">
         <v>123</v>
@@ -9442,7 +9520,7 @@
         <v>8.676666669999999</v>
       </c>
       <c r="AE51" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF51">
         <v>0.035556</v>
@@ -9495,10 +9573,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>45969.33102204861</v>
@@ -9519,16 +9597,16 @@
         <v>840</v>
       </c>
       <c r="I52" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L52" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M52">
         <v>130</v>
@@ -9585,7 +9663,7 @@
         <v>8.54466667</v>
       </c>
       <c r="AE52" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF52">
         <v>-0.014444</v>
@@ -9638,10 +9716,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2">
         <v>45969.33139809027</v>
@@ -9662,16 +9740,16 @@
         <v>870</v>
       </c>
       <c r="I53" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L53" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M53">
         <v>125</v>
@@ -9728,7 +9806,7 @@
         <v>8.757666670000001</v>
       </c>
       <c r="AE53" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF53">
         <v>0.023333</v>
@@ -9781,10 +9859,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C54" s="2">
         <v>45969.33144206018</v>
@@ -9805,16 +9883,16 @@
         <v>877</v>
       </c>
       <c r="I54" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M54">
         <v>131</v>
@@ -9871,7 +9949,7 @@
         <v>8.56983333</v>
       </c>
       <c r="AE54" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF54">
         <v>-0.010278</v>
@@ -9924,10 +10002,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C55" s="2">
         <v>45969.33172232639</v>
@@ -9948,16 +10026,16 @@
         <v>900</v>
       </c>
       <c r="I55" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L55" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M55">
         <v>129</v>
@@ -10014,7 +10092,7 @@
         <v>8.829333330000001</v>
       </c>
       <c r="AE55" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF55">
         <v>0.028333</v>
@@ -10067,10 +10145,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C56" s="2">
         <v>45969.33178894676</v>
@@ -10091,16 +10169,16 @@
         <v>907</v>
       </c>
       <c r="I56" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="M56">
         <v>128</v>
@@ -10157,7 +10235,7 @@
         <v>8.625999999999999</v>
       </c>
       <c r="AE56" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF56">
         <v>-0.022222</v>
@@ -10210,10 +10288,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>45969.33211010417</v>
@@ -10234,16 +10312,16 @@
         <v>930</v>
       </c>
       <c r="I57" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L57" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M57">
         <v>135</v>
@@ -10300,7 +10378,7 @@
         <v>8.36166667</v>
       </c>
       <c r="AE57" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF57">
         <v>-0.028889</v>
@@ -10353,10 +10431,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C58" s="2">
         <v>45969.33213626158</v>
@@ -10377,16 +10455,16 @@
         <v>937</v>
       </c>
       <c r="I58" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M58">
         <v>132</v>
@@ -10443,7 +10521,7 @@
         <v>8.524333329999999</v>
       </c>
       <c r="AE58" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF58">
         <v>0.017778</v>
@@ -10496,10 +10574,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2">
         <v>45969.3324109838</v>
@@ -10520,16 +10598,16 @@
         <v>960</v>
       </c>
       <c r="I59" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L59" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M59">
         <v>124</v>
@@ -10586,7 +10664,7 @@
         <v>8.503666669999999</v>
       </c>
       <c r="AE59" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF59">
         <v>-0.002222</v>
@@ -10639,10 +10717,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C60" s="2">
         <v>45969.33248328703</v>
@@ -10663,16 +10741,16 @@
         <v>967</v>
       </c>
       <c r="I60" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M60">
         <v>123</v>
@@ -10729,7 +10807,7 @@
         <v>8.574999999999999</v>
       </c>
       <c r="AE60" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF60">
         <v>0.007778</v>
@@ -10782,10 +10860,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>45969.33278709491</v>
@@ -10806,16 +10884,16 @@
         <v>990</v>
       </c>
       <c r="I61" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L61" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M61">
         <v>123</v>
@@ -10872,7 +10950,7 @@
         <v>8.321</v>
       </c>
       <c r="AE61" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF61">
         <v>-0.027778</v>
@@ -10925,10 +11003,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2">
         <v>45969.33283068287</v>
@@ -10949,16 +11027,16 @@
         <v>997</v>
       </c>
       <c r="I62" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L62" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M62">
         <v>126</v>
@@ -11015,7 +11093,7 @@
         <v>8.199</v>
       </c>
       <c r="AE62" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF62">
         <v>-0.013333</v>
@@ -11068,10 +11146,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>45969.33310554398</v>
@@ -11092,16 +11170,16 @@
         <v>1020</v>
       </c>
       <c r="I63" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M63">
         <v>128</v>
@@ -11158,7 +11236,7 @@
         <v>8.118</v>
       </c>
       <c r="AE63" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF63">
         <v>-0.008888999999999999</v>
@@ -11211,10 +11289,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2">
         <v>45969.33317813657</v>
@@ -11235,16 +11313,16 @@
         <v>1027</v>
       </c>
       <c r="I64" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L64" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M64">
         <v>121</v>
@@ -11301,7 +11379,7 @@
         <v>7.91466667</v>
       </c>
       <c r="AE64" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF64">
         <v>-0.022222</v>
@@ -11354,10 +11432,10 @@
     </row>
     <row r="65" spans="1:48">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>45969.3334815625</v>
@@ -11378,16 +11456,16 @@
         <v>1050</v>
       </c>
       <c r="I65" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L65" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M65">
         <v>121</v>
@@ -11444,7 +11522,7 @@
         <v>7.91466667</v>
       </c>
       <c r="AE65" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF65">
         <v>0</v>
@@ -11497,10 +11575,10 @@
     </row>
     <row r="66" spans="1:48">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C66" s="2">
         <v>45969.33352534723</v>
@@ -11521,16 +11599,16 @@
         <v>1057</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="M66">
         <v>118</v>
@@ -11587,7 +11665,7 @@
         <v>8.08733333</v>
       </c>
       <c r="AE66" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF66">
         <v>0.018889</v>
@@ -11640,10 +11718,10 @@
     </row>
     <row r="67" spans="1:48">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>45969.33380033565</v>
@@ -11664,16 +11742,16 @@
         <v>1080</v>
       </c>
       <c r="I67" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L67" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="M67">
         <v>114</v>
@@ -11730,7 +11808,7 @@
         <v>7.60966667</v>
       </c>
       <c r="AE67" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF67">
         <v>-0.052222</v>
@@ -11783,10 +11861,10 @@
     </row>
     <row r="68" spans="1:48">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2">
         <v>45969.3338719213</v>
@@ -11807,16 +11885,16 @@
         <v>1087</v>
       </c>
       <c r="I68" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M68">
         <v>122</v>
@@ -11873,7 +11951,7 @@
         <v>7.59966667</v>
       </c>
       <c r="AE68" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF68">
         <v>-0.001111</v>
@@ -11926,10 +12004,10 @@
     </row>
     <row r="69" spans="1:48">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>45969.33417618056</v>
@@ -11950,16 +12028,16 @@
         <v>1110</v>
       </c>
       <c r="I69" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M69">
         <v>115</v>
@@ -12016,7 +12094,7 @@
         <v>7.65066667</v>
       </c>
       <c r="AE69" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF69">
         <v>0.005556</v>
@@ -12069,10 +12147,10 @@
     </row>
     <row r="70" spans="1:48">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2">
         <v>45969.33421924768</v>
@@ -12093,16 +12171,16 @@
         <v>1117</v>
       </c>
       <c r="I70" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M70">
         <v>120</v>
@@ -12159,7 +12237,7 @@
         <v>7.559</v>
       </c>
       <c r="AE70" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF70">
         <v>-0.01</v>
@@ -12212,10 +12290,10 @@
     </row>
     <row r="71" spans="1:48">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C71" s="2">
         <v>45969.33449423611</v>
@@ -12236,16 +12314,16 @@
         <v>1140</v>
       </c>
       <c r="I71" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L71" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M71">
         <v>114</v>
@@ -12302,7 +12380,7 @@
         <v>8.20933333</v>
       </c>
       <c r="AE71" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF71">
         <v>0.07111099999999999</v>
@@ -12353,15 +12431,15 @@
         <v>8.447695</v>
       </c>
       <c r="AV71" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="1:48">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C72" s="2">
         <v>45969.33456671296</v>
@@ -12382,16 +12460,16 @@
         <v>1147</v>
       </c>
       <c r="I72" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M72">
         <v>116</v>
@@ -12448,7 +12526,7 @@
         <v>8.341333329999999</v>
       </c>
       <c r="AE72" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF72">
         <v>0.014444</v>
@@ -12501,10 +12579,10 @@
     </row>
     <row r="73" spans="1:48">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C73" s="2">
         <v>45969.33491418981</v>
@@ -12525,16 +12603,16 @@
         <v>1177</v>
       </c>
       <c r="I73" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L73" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M73">
         <v>125</v>
@@ -12591,7 +12669,7 @@
         <v>7.95533333</v>
       </c>
       <c r="AE73" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF73">
         <v>-0.042222</v>
@@ -12644,10 +12722,10 @@
     </row>
     <row r="74" spans="1:48">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C74" s="2">
         <v>45969.33526122685</v>
@@ -12668,16 +12746,16 @@
         <v>1207</v>
       </c>
       <c r="I74" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L74" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M74">
         <v>117</v>
@@ -12734,7 +12812,7 @@
         <v>8.625999999999999</v>
       </c>
       <c r="AE74" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF74">
         <v>0.073333</v>
@@ -12787,10 +12865,10 @@
     </row>
     <row r="75" spans="1:48">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C75" s="2">
         <v>45969.33560809028</v>
@@ -12811,16 +12889,16 @@
         <v>1237</v>
       </c>
       <c r="I75" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M75">
         <v>120</v>
@@ -12877,7 +12955,7 @@
         <v>8.006</v>
       </c>
       <c r="AE75" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF75">
         <v>-0.067778</v>
@@ -12930,10 +13008,10 @@
     </row>
     <row r="76" spans="1:48">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C76" s="2">
         <v>45969.33630322917</v>
@@ -12954,16 +13032,16 @@
         <v>1297</v>
       </c>
       <c r="I76" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L76" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M76">
         <v>117</v>
@@ -13020,7 +13098,7 @@
         <v>8.7325</v>
       </c>
       <c r="AE76" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF76">
         <v>0.039722</v>
@@ -13073,10 +13151,10 @@
     </row>
     <row r="77" spans="1:48">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C77" s="2">
         <v>45969.33665033564</v>
@@ -13097,16 +13175,16 @@
         <v>1327</v>
       </c>
       <c r="I77" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L77" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M77">
         <v>112</v>
@@ -13163,7 +13241,7 @@
         <v>8.961</v>
       </c>
       <c r="AE77" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF77">
         <v>0.025</v>
@@ -13216,10 +13294,10 @@
     </row>
     <row r="78" spans="1:48">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C78" s="2">
         <v>45969.33699708333</v>
@@ -13240,16 +13318,16 @@
         <v>1357</v>
       </c>
       <c r="I78" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L78" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M78">
         <v>112</v>
@@ -13306,7 +13384,7 @@
         <v>9.24566667</v>
       </c>
       <c r="AE78" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF78">
         <v>0.031111</v>
@@ -13359,10 +13437,10 @@
     </row>
     <row r="79" spans="1:48">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C79" s="2">
         <v>45969.3373444213</v>
@@ -13383,16 +13461,16 @@
         <v>1387</v>
       </c>
       <c r="I79" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L79" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M79">
         <v>108</v>
@@ -13449,7 +13527,7 @@
         <v>9.083</v>
       </c>
       <c r="AE79" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF79">
         <v>-0.017778</v>
@@ -13502,10 +13580,10 @@
     </row>
     <row r="80" spans="1:48">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2">
         <v>45969.33769148148</v>
@@ -13526,16 +13604,16 @@
         <v>1417</v>
       </c>
       <c r="I80" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L80" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="M80">
         <v>107</v>
@@ -13592,7 +13670,7 @@
         <v>9.449</v>
       </c>
       <c r="AE80" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF80">
         <v>0.04</v>
@@ -13645,10 +13723,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C81" s="2">
         <v>45969.33803916667</v>
@@ -13669,16 +13747,16 @@
         <v>1447</v>
       </c>
       <c r="I81" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L81" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="M81">
         <v>122</v>
@@ -13735,7 +13813,7 @@
         <v>9.763666669999999</v>
       </c>
       <c r="AE81" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF81">
         <v>0.034444</v>
@@ -13788,10 +13866,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C82" s="2">
         <v>45969.33838612268</v>
@@ -13812,16 +13890,16 @@
         <v>1477</v>
       </c>
       <c r="I82" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M82">
         <v>129</v>
@@ -13878,7 +13956,7 @@
         <v>9.99733333</v>
       </c>
       <c r="AE82" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF82">
         <v>0.025556</v>
@@ -13931,10 +14009,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2">
         <v>45969.33873334491</v>
@@ -13955,16 +14033,16 @@
         <v>1507</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L83" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="M83">
         <v>106</v>
@@ -14021,7 +14099,7 @@
         <v>9.692666669999999</v>
       </c>
       <c r="AE83" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF83">
         <v>-0.033333</v>
@@ -14074,10 +14152,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2">
         <v>45969.33908527778</v>
@@ -14098,16 +14176,16 @@
         <v>1537</v>
       </c>
       <c r="I84" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L84" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="M84">
         <v>110</v>
@@ -14164,7 +14242,7 @@
         <v>8.97133333</v>
       </c>
       <c r="AE84" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF84">
         <v>-0.078889</v>
@@ -14217,10 +14295,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C85" s="2">
         <v>45969.33942775463</v>
@@ -14241,16 +14319,16 @@
         <v>1567</v>
       </c>
       <c r="I85" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L85" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M85">
         <v>119</v>
@@ -14307,7 +14385,7 @@
         <v>9.134</v>
       </c>
       <c r="AE85" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF85">
         <v>0.017778</v>
@@ -14360,10 +14438,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C86" s="2">
         <v>45969.33977502315</v>
@@ -14384,16 +14462,16 @@
         <v>1597</v>
       </c>
       <c r="I86" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L86" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="M86">
         <v>123</v>
@@ -14450,7 +14528,7 @@
         <v>9.07266667</v>
       </c>
       <c r="AE86" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF86">
         <v>-0.006667</v>
@@ -14503,10 +14581,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C87" s="2">
         <v>45969.3404693287</v>
@@ -14527,16 +14605,16 @@
         <v>1657</v>
       </c>
       <c r="I87" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L87" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="M87">
         <v>122</v>
@@ -14593,7 +14671,7 @@
         <v>9.067833329999999</v>
       </c>
       <c r="AE87" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF87">
         <v>-0.000278</v>
@@ -14646,10 +14724,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C88" s="2">
         <v>45969.34081684027</v>
@@ -14670,16 +14748,16 @@
         <v>1687</v>
       </c>
       <c r="I88" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L88" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M88">
         <v>121</v>
@@ -14736,7 +14814,7 @@
         <v>10.27166667</v>
       </c>
       <c r="AE88" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF88">
         <v>0.131667</v>
@@ -14789,10 +14867,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C89" s="2">
         <v>45969.34116405093</v>
@@ -14813,16 +14891,16 @@
         <v>1717</v>
       </c>
       <c r="I89" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L89" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M89">
         <v>104</v>
@@ -14879,7 +14957,7 @@
         <v>9.418333329999999</v>
       </c>
       <c r="AE89" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF89">
         <v>-0.093333</v>
@@ -14932,10 +15010,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C90" s="2">
         <v>45969.34151090278</v>
@@ -14956,16 +15034,16 @@
         <v>1747</v>
       </c>
       <c r="I90" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L90" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M90">
         <v>95</v>
@@ -15022,7 +15100,7 @@
         <v>10.29233333</v>
       </c>
       <c r="AE90" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF90">
         <v>0.095556</v>
@@ -15075,10 +15153,10 @@
     </row>
     <row r="91" spans="1:47">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C91" s="2">
         <v>45969.34185826389</v>
@@ -15099,16 +15177,16 @@
         <v>1777</v>
       </c>
       <c r="I91" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L91" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="M91">
         <v>113</v>
@@ -15165,7 +15243,7 @@
         <v>10.01766667</v>
       </c>
       <c r="AE91" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF91">
         <v>-0.03</v>
@@ -15218,10 +15296,10 @@
     </row>
     <row r="92" spans="1:47">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C92" s="2">
         <v>45969.34220559028</v>
@@ -15242,16 +15320,16 @@
         <v>1807</v>
       </c>
       <c r="I92" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M92">
         <v>114</v>
@@ -15308,7 +15386,7 @@
         <v>8.48366667</v>
       </c>
       <c r="AE92" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF92">
         <v>-0.167778</v>
@@ -15361,10 +15439,10 @@
     </row>
     <row r="93" spans="1:47">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C93" s="2">
         <v>45969.34255259259</v>
@@ -15385,16 +15463,16 @@
         <v>1837</v>
       </c>
       <c r="I93" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L93" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M93">
         <v>126</v>
@@ -15451,7 +15529,7 @@
         <v>10.739</v>
       </c>
       <c r="AE93" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF93">
         <v>0.246667</v>
@@ -15504,10 +15582,10 @@
     </row>
     <row r="94" spans="1:47">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2">
         <v>45969.34289959491</v>
@@ -15528,16 +15606,16 @@
         <v>1867</v>
       </c>
       <c r="I94" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L94" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="M94">
         <v>110</v>
@@ -15594,7 +15672,7 @@
         <v>10.05833333</v>
       </c>
       <c r="AE94" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF94">
         <v>-0.074444</v>
@@ -15647,10 +15725,10 @@
     </row>
     <row r="95" spans="1:47">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C95" s="2">
         <v>45969.34324704861</v>
@@ -15671,16 +15749,16 @@
         <v>1897</v>
       </c>
       <c r="I95" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L95" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M95">
         <v>126</v>
@@ -15737,7 +15815,7 @@
         <v>9.31666667</v>
       </c>
       <c r="AE95" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF95">
         <v>-0.081111</v>
@@ -15790,10 +15868,10 @@
     </row>
     <row r="96" spans="1:47">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C96" s="2">
         <v>45969.34394149305</v>
@@ -15814,16 +15892,16 @@
         <v>1957</v>
       </c>
       <c r="I96" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L96" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M96">
         <v>144</v>
@@ -15880,7 +15958,7 @@
         <v>9.418333329999999</v>
       </c>
       <c r="AE96" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF96">
         <v>0.005556</v>
@@ -15933,10 +16011,10 @@
     </row>
     <row r="97" spans="1:48">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C97" s="2">
         <v>45969.34428871528</v>
@@ -15957,16 +16035,16 @@
         <v>1987</v>
       </c>
       <c r="I97" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L97" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M97">
         <v>142</v>
@@ -16023,7 +16101,7 @@
         <v>11.14566667</v>
       </c>
       <c r="AE97" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF97">
         <v>0.188889</v>
@@ -16076,10 +16154,10 @@
     </row>
     <row r="98" spans="1:48">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C98" s="2">
         <v>45969.34463613426</v>
@@ -16100,16 +16178,16 @@
         <v>2017</v>
       </c>
       <c r="I98" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L98" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="M98">
         <v>175</v>
@@ -16166,7 +16244,7 @@
         <v>12.08033333</v>
       </c>
       <c r="AE98" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF98">
         <v>0.102222</v>
@@ -16219,10 +16297,10 @@
     </row>
     <row r="99" spans="1:48">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C99" s="2">
         <v>45969.34498329861</v>
@@ -16243,16 +16321,16 @@
         <v>2047</v>
       </c>
       <c r="I99" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L99" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="M99">
         <v>78</v>
@@ -16309,7 +16387,7 @@
         <v>10.01766667</v>
       </c>
       <c r="AE99" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF99">
         <v>-0.225556</v>
@@ -16362,10 +16440,10 @@
     </row>
     <row r="100" spans="1:48">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C100" s="2">
         <v>45969.34533060185</v>
@@ -16386,16 +16464,16 @@
         <v>2077</v>
       </c>
       <c r="I100" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L100" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="M100">
         <v>61</v>
@@ -16452,7 +16530,7 @@
         <v>8.290333329999999</v>
       </c>
       <c r="AE100" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF100">
         <v>-0.188889</v>
@@ -16505,10 +16583,10 @@
     </row>
     <row r="101" spans="1:48">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C101" s="2">
         <v>45969.34567725695</v>
@@ -16529,16 +16607,16 @@
         <v>2107</v>
       </c>
       <c r="I101" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L101" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="M101">
         <v>102</v>
@@ -16595,7 +16673,7 @@
         <v>8.158666670000001</v>
       </c>
       <c r="AE101" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF101">
         <v>-0.014444</v>
@@ -16648,10 +16726,10 @@
     </row>
     <row r="102" spans="1:48">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C102" s="2">
         <v>45969.34602481481</v>
@@ -16672,16 +16750,16 @@
         <v>2137</v>
       </c>
       <c r="I102" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="L102" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M102">
         <v>167</v>
@@ -16738,7 +16816,7 @@
         <v>10.83066667</v>
       </c>
       <c r="AE102" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF102">
         <v>0.292222</v>
@@ -16791,10 +16869,10 @@
     </row>
     <row r="103" spans="1:48">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C103" s="2">
         <v>45969.34671930555</v>
@@ -16815,16 +16893,16 @@
         <v>2197</v>
       </c>
       <c r="I103" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L103" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="M103">
         <v>101</v>
@@ -16881,7 +16959,7 @@
         <v>9.17433333</v>
       </c>
       <c r="AE103" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF103">
         <v>-0.090556</v>
@@ -16934,10 +17012,10 @@
     </row>
     <row r="104" spans="1:48">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C104" s="2">
         <v>45969.34706663194</v>
@@ -16958,16 +17036,16 @@
         <v>2227</v>
       </c>
       <c r="I104" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J104" t="b">
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L104" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="M104">
         <v>22</v>
@@ -17024,7 +17102,7 @@
         <v>9.28633333</v>
       </c>
       <c r="AE104" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF104">
         <v>0.012222</v>
@@ -17077,10 +17155,10 @@
     </row>
     <row r="105" spans="1:48">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C105" s="2">
         <v>45969.34741402778</v>
@@ -17101,16 +17179,16 @@
         <v>2257</v>
       </c>
       <c r="I105" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L105" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M105">
         <v>53</v>
@@ -17167,7 +17245,7 @@
         <v>8.341333329999999</v>
       </c>
       <c r="AE105" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF105">
         <v>-0.103333</v>
@@ -17220,10 +17298,10 @@
     </row>
     <row r="106" spans="1:48">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C106" s="2">
         <v>45969.34776096065</v>
@@ -17244,16 +17322,16 @@
         <v>2287</v>
       </c>
       <c r="I106" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J106" t="b">
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="L106" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M106">
         <v>159</v>
@@ -17310,7 +17388,7 @@
         <v>8.372</v>
       </c>
       <c r="AE106" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF106">
         <v>0.003333</v>
@@ -17363,10 +17441,10 @@
     </row>
     <row r="107" spans="1:48">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C107" s="2">
         <v>45969.34810806713</v>
@@ -17387,16 +17465,16 @@
         <v>2317</v>
       </c>
       <c r="I107" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="M107">
         <v>174</v>
@@ -17453,7 +17531,7 @@
         <v>10.922</v>
       </c>
       <c r="AE107" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF107">
         <v>0.278889</v>
@@ -17506,10 +17584,10 @@
     </row>
     <row r="108" spans="1:48">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C108" s="2">
         <v>45969.34845541666</v>
@@ -17530,16 +17608,16 @@
         <v>2347</v>
       </c>
       <c r="I108" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J108" t="b">
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L108" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M108">
         <v>153</v>
@@ -17596,7 +17674,7 @@
         <v>8.757999999999999</v>
       </c>
       <c r="AE108" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AF108">
         <v>-0.236667</v>
@@ -17649,10 +17727,10 @@
     </row>
     <row r="109" spans="1:48">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C109" s="2">
         <v>45969.35019151621</v>
@@ -17673,16 +17751,16 @@
         <v>2497</v>
       </c>
       <c r="I109" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J109" t="b">
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="L109" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M109">
         <v>175</v>
@@ -17739,7 +17817,7 @@
         <v>8.833066669999999</v>
       </c>
       <c r="AE109" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF109">
         <v>0.001644</v>
@@ -17790,15 +17868,15 @@
         <v>8.255542</v>
       </c>
       <c r="AV109" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
     </row>
     <row r="110" spans="1:48">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C110" s="2">
         <v>45969.35053877315</v>
@@ -17819,16 +17897,16 @@
         <v>2527</v>
       </c>
       <c r="I110" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J110" t="b">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="L110" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M110">
         <v>177</v>
@@ -17885,7 +17963,7 @@
         <v>8.097666670000001</v>
       </c>
       <c r="AE110" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF110">
         <v>-0.080444</v>
@@ -17938,10 +18016,10 @@
     </row>
     <row r="111" spans="1:48">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C111" s="2">
         <v>45969.35088596064</v>
@@ -17962,16 +18040,16 @@
         <v>2557</v>
       </c>
       <c r="I111" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J111" t="b">
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L111" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="M111">
         <v>109</v>
@@ -18028,7 +18106,7 @@
         <v>7.85366667</v>
       </c>
       <c r="AE111" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF111">
         <v>-0.026667</v>
@@ -18081,10 +18159,10 @@
     </row>
     <row r="112" spans="1:48">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C112" s="2">
         <v>45969.35192736111</v>
@@ -18105,16 +18183,16 @@
         <v>2647</v>
       </c>
       <c r="I112" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J112" t="b">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L112" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="M112">
         <v>166</v>
@@ -18171,7 +18249,7 @@
         <v>7.62333333</v>
       </c>
       <c r="AE112" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF112">
         <v>-0.008395</v>
@@ -18224,10 +18302,10 @@
     </row>
     <row r="113" spans="1:47">
       <c r="A113" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C113" s="2">
         <v>45969.35227456019</v>
@@ -18248,16 +18326,16 @@
         <v>2677</v>
       </c>
       <c r="I113" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
       </c>
       <c r="K113" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="L113" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="M113">
         <v>131</v>
@@ -18314,7 +18392,7 @@
         <v>7.44733333</v>
       </c>
       <c r="AE113" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF113">
         <v>-0.019259</v>
@@ -18367,10 +18445,10 @@
     </row>
     <row r="114" spans="1:47">
       <c r="A114" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C114" s="2">
         <v>45969.35262180556</v>
@@ -18391,16 +18469,16 @@
         <v>2707</v>
       </c>
       <c r="I114" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J114" t="b">
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="L114" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M114">
         <v>139</v>
@@ -18457,7 +18535,7 @@
         <v>6.82766667</v>
       </c>
       <c r="AE114" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF114">
         <v>-0.067778</v>
@@ -18510,10 +18588,10 @@
     </row>
     <row r="115" spans="1:47">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C115" s="2">
         <v>45969.35366327546</v>
@@ -18534,16 +18612,16 @@
         <v>2797</v>
       </c>
       <c r="I115" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J115" t="b">
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="L115" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M115">
         <v>226</v>
@@ -18600,7 +18678,7 @@
         <v>7.37611111</v>
       </c>
       <c r="AE115" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF115">
         <v>0.02</v>
@@ -18653,10 +18731,10 @@
     </row>
     <row r="116" spans="1:47">
       <c r="A116" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C116" s="2">
         <v>45969.3540109375</v>
@@ -18677,16 +18755,16 @@
         <v>2827</v>
       </c>
       <c r="I116" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L116" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M116">
         <v>95</v>
@@ -18743,7 +18821,7 @@
         <v>8.372</v>
       </c>
       <c r="AE116" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF116">
         <v>0.108889</v>
@@ -18796,10 +18874,10 @@
     </row>
     <row r="117" spans="1:47">
       <c r="A117" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B117" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C117" s="2">
         <v>45969.35435817129</v>
@@ -18820,16 +18898,16 @@
         <v>2857</v>
       </c>
       <c r="I117" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J117" t="b">
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L117" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="M117">
         <v>284</v>
@@ -18886,7 +18964,7 @@
         <v>8.23966667</v>
       </c>
       <c r="AE117" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF117">
         <v>-0.014444</v>
@@ -18939,10 +19017,10 @@
     </row>
     <row r="118" spans="1:47">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C118" s="2">
         <v>45969.35470891204</v>
@@ -18963,16 +19041,16 @@
         <v>2887</v>
       </c>
       <c r="I118" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J118" t="b">
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="L118" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M118">
         <v>94</v>
@@ -19029,7 +19107,7 @@
         <v>8.31066667</v>
       </c>
       <c r="AE118" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF118">
         <v>0.007778</v>
@@ -19082,10 +19160,10 @@
     </row>
     <row r="119" spans="1:47">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C119" s="2">
         <v>45969.35505239583</v>
@@ -19106,16 +19184,16 @@
         <v>2917</v>
       </c>
       <c r="I119" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J119" t="b">
         <v>1</v>
       </c>
       <c r="K119" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L119" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="M119">
         <v>333</v>
@@ -19172,7 +19250,7 @@
         <v>7.75233333</v>
       </c>
       <c r="AE119" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF119">
         <v>-0.061111</v>
@@ -19225,10 +19303,10 @@
     </row>
     <row r="120" spans="1:47">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C120" s="2">
         <v>45969.3553999537</v>
@@ -19249,16 +19327,16 @@
         <v>2947</v>
       </c>
       <c r="I120" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J120" t="b">
         <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="L120" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M120">
         <v>94</v>
@@ -19315,7 +19393,7 @@
         <v>7.498</v>
       </c>
       <c r="AE120" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF120">
         <v>-0.027778</v>
@@ -19368,10 +19446,10 @@
     </row>
     <row r="121" spans="1:47">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B121" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C121" s="2">
         <v>45969.35644128472</v>
@@ -19392,16 +19470,16 @@
         <v>3037</v>
       </c>
       <c r="I121" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J121" t="b">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="L121" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M121">
         <v>135</v>
@@ -19458,7 +19536,7 @@
         <v>7.12555556</v>
       </c>
       <c r="AE121" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF121">
         <v>-0.01358</v>
@@ -19511,10 +19589,10 @@
     </row>
     <row r="122" spans="1:47">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B122" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C122" s="2">
         <v>45969.35678886574</v>
@@ -19535,16 +19613,16 @@
         <v>3067</v>
       </c>
       <c r="I122" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J122" t="b">
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="L122" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="M122">
         <v>177</v>
@@ -19601,7 +19679,7 @@
         <v>7.752</v>
       </c>
       <c r="AE122" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF122">
         <v>0.068519</v>
@@ -19654,10 +19732,10 @@
     </row>
     <row r="123" spans="1:47">
       <c r="A123" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C123" s="2">
         <v>45969.35713583334</v>
@@ -19678,16 +19756,16 @@
         <v>3097</v>
       </c>
       <c r="I123" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
       </c>
       <c r="K123" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="L123" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="M123">
         <v>136</v>
@@ -19744,7 +19822,7 @@
         <v>7.945</v>
       </c>
       <c r="AE123" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF123">
         <v>0.021111</v>
@@ -19797,10 +19875,10 @@
     </row>
     <row r="124" spans="1:47">
       <c r="A124" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B124" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C124" s="2">
         <v>45969.35748295139</v>
@@ -19821,16 +19899,16 @@
         <v>3127</v>
       </c>
       <c r="I124" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J124" t="b">
         <v>1</v>
       </c>
       <c r="K124" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="L124" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="M124">
         <v>229</v>
@@ -19887,7 +19965,7 @@
         <v>8.13833333</v>
       </c>
       <c r="AE124" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AF124">
         <v>0.021111</v>
@@ -19950,156 +20028,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2">
         <v>45969.3588721875</v>
@@ -20120,16 +20198,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="L2" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="M2">
         <v>186</v>
@@ -20186,7 +20264,7 @@
         <v>-24.03091667</v>
       </c>
       <c r="AE2" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AG2">
         <v>-78.841667</v>
@@ -20203,10 +20281,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>45969.3592909375</v>
@@ -20227,16 +20305,16 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="L3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="M3">
         <v>163</v>
@@ -20293,7 +20371,7 @@
         <v>-25.68466667</v>
       </c>
       <c r="AE3" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF3">
         <v>-0.180833</v>
@@ -20334,10 +20412,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2">
         <v>45969.3595668287</v>
@@ -20358,16 +20436,16 @@
         <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L4" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="M4">
         <v>136</v>
@@ -20424,7 +20502,7 @@
         <v>-25.17633333</v>
       </c>
       <c r="AE4" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF4">
         <v>0.055556</v>
@@ -20477,10 +20555,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2">
         <v>45969.35991387731</v>
@@ -20501,16 +20579,16 @@
         <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="L5" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="M5">
         <v>140</v>
@@ -20567,7 +20645,7 @@
         <v>-24.14033333</v>
       </c>
       <c r="AE5" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF5">
         <v>0.113333</v>
@@ -20620,10 +20698,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2">
         <v>45969.36026076389</v>
@@ -20644,16 +20722,16 @@
         <v>120</v>
       </c>
       <c r="I6" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="L6" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="M6">
         <v>229</v>
@@ -20710,7 +20788,7 @@
         <v>-21.92533333</v>
       </c>
       <c r="AE6" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF6">
         <v>0.242222</v>
@@ -20763,10 +20841,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2">
         <v>45969.36060825232</v>
@@ -20787,16 +20865,16 @@
         <v>150</v>
       </c>
       <c r="I7" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="L7" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="M7">
         <v>194</v>
@@ -20853,7 +20931,7 @@
         <v>-20.74666667</v>
       </c>
       <c r="AE7" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF7">
         <v>0.128889</v>
@@ -20906,10 +20984,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2">
         <v>45969.36095511574</v>
@@ -20930,16 +21008,16 @@
         <v>180</v>
       </c>
       <c r="I8" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="L8" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="M8">
         <v>70</v>
@@ -20996,7 +21074,7 @@
         <v>-20.452</v>
       </c>
       <c r="AE8" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF8">
         <v>0.032222</v>
@@ -21049,10 +21127,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2">
         <v>45969.36130256944</v>
@@ -21073,16 +21151,16 @@
         <v>210</v>
       </c>
       <c r="I9" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="L9" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="M9">
         <v>161</v>
@@ -21139,7 +21217,7 @@
         <v>-19.38533333</v>
       </c>
       <c r="AE9" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF9">
         <v>0.116667</v>
@@ -21192,10 +21270,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>45969.36165010417</v>
@@ -21216,16 +21294,16 @@
         <v>240</v>
       </c>
       <c r="I10" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="L10" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="M10">
         <v>41</v>
@@ -21282,7 +21360,7 @@
         <v>-18.01366667</v>
       </c>
       <c r="AE10" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF10">
         <v>0.15</v>
@@ -21335,10 +21413,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>45969.3619968287</v>
@@ -21359,16 +21437,16 @@
         <v>270</v>
       </c>
       <c r="I11" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="L11" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="M11">
         <v>84</v>
@@ -21425,7 +21503,7 @@
         <v>-16.36766667</v>
       </c>
       <c r="AE11" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF11">
         <v>0.18</v>
@@ -21478,10 +21556,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2">
         <v>45969.36234449074</v>
@@ -21502,16 +21580,16 @@
         <v>300</v>
       </c>
       <c r="I12" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="L12" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M12">
         <v>179</v>
@@ -21568,7 +21646,7 @@
         <v>-15.88</v>
       </c>
       <c r="AE12" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF12">
         <v>0.053333</v>
@@ -21621,10 +21699,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2">
         <v>45969.36269141204</v>
@@ -21645,16 +21723,16 @@
         <v>330</v>
       </c>
       <c r="I13" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="L13" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="M13">
         <v>147</v>
@@ -21711,7 +21789,7 @@
         <v>-15.11833333</v>
       </c>
       <c r="AE13" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF13">
         <v>0.083333</v>
@@ -21764,10 +21842,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2">
         <v>45969.36303857639</v>
@@ -21788,16 +21866,16 @@
         <v>360</v>
       </c>
       <c r="I14" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="L14" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="M14">
         <v>147</v>
@@ -21854,7 +21932,7 @@
         <v>-14.112</v>
       </c>
       <c r="AE14" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF14">
         <v>0.11</v>
@@ -21907,10 +21985,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>45969.36338596065</v>
@@ -21931,16 +22009,16 @@
         <v>390</v>
       </c>
       <c r="I15" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="L15" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="M15">
         <v>118</v>
@@ -21997,7 +22075,7 @@
         <v>-13.401</v>
       </c>
       <c r="AE15" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF15">
         <v>0.077778</v>
@@ -22050,10 +22128,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2">
         <v>45969.36373300926</v>
@@ -22074,16 +22152,16 @@
         <v>420</v>
       </c>
       <c r="I16" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="L16" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="M16">
         <v>105</v>
@@ -22140,7 +22218,7 @@
         <v>-13.10666667</v>
       </c>
       <c r="AE16" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF16">
         <v>0.032222</v>
@@ -22193,10 +22271,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2">
         <v>45969.36408025463</v>
@@ -22217,16 +22295,16 @@
         <v>450</v>
       </c>
       <c r="I17" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="L17" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="M17">
         <v>125</v>
@@ -22283,7 +22361,7 @@
         <v>-12.54733333</v>
       </c>
       <c r="AE17" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF17">
         <v>0.061111</v>
@@ -22336,10 +22414,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2">
         <v>45969.36442775463</v>
@@ -22360,16 +22438,16 @@
         <v>480</v>
       </c>
       <c r="I18" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="L18" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="M18">
         <v>120</v>
@@ -22426,7 +22504,7 @@
         <v>-12.436</v>
       </c>
       <c r="AE18" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF18">
         <v>0.012222</v>
@@ -22479,10 +22557,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2">
         <v>45969.36477454861</v>
@@ -22503,16 +22581,16 @@
         <v>510</v>
       </c>
       <c r="I19" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="L19" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="M19">
         <v>102</v>
@@ -22569,7 +22647,7 @@
         <v>-11.88733333</v>
       </c>
       <c r="AE19" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF19">
         <v>0.06</v>
@@ -22622,10 +22700,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2">
         <v>45969.36512233796</v>
@@ -22646,16 +22724,16 @@
         <v>540</v>
       </c>
       <c r="I20" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="L20" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -22712,7 +22790,7 @@
         <v>-11.03366667</v>
       </c>
       <c r="AE20" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF20">
         <v>0.093333</v>
@@ -22765,10 +22843,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C21" s="2">
         <v>45969.36547962963</v>
@@ -22789,16 +22867,16 @@
         <v>570</v>
       </c>
       <c r="I21" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="L21" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="M21">
         <v>121</v>
@@ -22855,7 +22933,7 @@
         <v>-10.88133333</v>
       </c>
       <c r="AE21" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF21">
         <v>0.016667</v>
@@ -22908,10 +22986,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2">
         <v>45969.36581638889</v>
@@ -22932,16 +23010,16 @@
         <v>600</v>
       </c>
       <c r="I22" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="L22" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="M22">
         <v>128</v>
@@ -22998,7 +23076,7 @@
         <v>-10.71866667</v>
       </c>
       <c r="AE22" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF22">
         <v>0.017778</v>
@@ -23051,10 +23129,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2">
         <v>45969.36616380787</v>
@@ -23075,16 +23153,16 @@
         <v>630</v>
       </c>
       <c r="I23" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="L23" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="M23">
         <v>116</v>
@@ -23141,7 +23219,7 @@
         <v>-10.15</v>
       </c>
       <c r="AE23" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF23">
         <v>0.062222</v>
@@ -23194,10 +23272,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2">
         <v>45969.36651113426</v>
@@ -23218,16 +23296,16 @@
         <v>660</v>
       </c>
       <c r="I24" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L24" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="M24">
         <v>114</v>
@@ -23284,7 +23362,7 @@
         <v>-10.18033333</v>
       </c>
       <c r="AE24" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF24">
         <v>-0.003333</v>
@@ -23337,10 +23415,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2">
         <v>45969.36685846065</v>
@@ -23361,16 +23439,16 @@
         <v>690</v>
       </c>
       <c r="I25" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="L25" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="M25">
         <v>121</v>
@@ -23427,7 +23505,7 @@
         <v>-10.414</v>
       </c>
       <c r="AE25" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF25">
         <v>-0.025556</v>
@@ -23480,10 +23558,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2">
         <v>45969.36720564814</v>
@@ -23504,16 +23582,16 @@
         <v>720</v>
       </c>
       <c r="I26" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="L26" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="M26">
         <v>106</v>
@@ -23570,7 +23648,7 @@
         <v>-9.967000000000001</v>
       </c>
       <c r="AE26" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF26">
         <v>0.048889</v>
@@ -23623,10 +23701,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2">
         <v>45969.36755239583</v>
@@ -23647,16 +23725,16 @@
         <v>750</v>
       </c>
       <c r="I27" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="L27" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="M27">
         <v>118</v>
@@ -23713,7 +23791,7 @@
         <v>-9.99733333</v>
       </c>
       <c r="AE27" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF27">
         <v>-0.003333</v>
@@ -23766,10 +23844,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>45969.36789958333</v>
@@ -23790,16 +23868,16 @@
         <v>780</v>
       </c>
       <c r="I28" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="L28" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M28">
         <v>112</v>
@@ -23856,7 +23934,7 @@
         <v>-10.028</v>
       </c>
       <c r="AE28" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF28">
         <v>-0.003333</v>
@@ -23909,10 +23987,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2">
         <v>45969.36824732639</v>
@@ -23933,16 +24011,16 @@
         <v>810</v>
       </c>
       <c r="I29" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="L29" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M29">
         <v>98</v>
@@ -23999,7 +24077,7 @@
         <v>-9.50966667</v>
       </c>
       <c r="AE29" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF29">
         <v>0.056667</v>
@@ -24052,10 +24130,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>45969.36859418981</v>
@@ -24076,16 +24154,16 @@
         <v>840</v>
       </c>
       <c r="I30" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="L30" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="M30">
         <v>115</v>
@@ -24142,7 +24220,7 @@
         <v>-9.276</v>
       </c>
       <c r="AE30" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF30">
         <v>0.025556</v>
@@ -24195,10 +24273,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2">
         <v>45969.36894174769</v>
@@ -24219,16 +24297,16 @@
         <v>870</v>
       </c>
       <c r="I31" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="L31" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="M31">
         <v>107</v>
@@ -24285,7 +24363,7 @@
         <v>-9.022</v>
       </c>
       <c r="AE31" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF31">
         <v>0.027778</v>
@@ -24338,10 +24416,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2">
         <v>45969.36929376157</v>
@@ -24362,16 +24440,16 @@
         <v>900</v>
       </c>
       <c r="I32" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L32" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="M32">
         <v>108</v>
@@ -24428,7 +24506,7 @@
         <v>-8.625999999999999</v>
       </c>
       <c r="AE32" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF32">
         <v>0.043333</v>
@@ -24481,10 +24559,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2">
         <v>45969.36963592593</v>
@@ -24505,16 +24583,16 @@
         <v>930</v>
       </c>
       <c r="I33" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="L33" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="M33">
         <v>107</v>
@@ -24571,7 +24649,7 @@
         <v>-8.199</v>
       </c>
       <c r="AE33" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF33">
         <v>0.046667</v>
@@ -24624,10 +24702,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2">
         <v>45969.36998349537</v>
@@ -24648,16 +24726,16 @@
         <v>960</v>
       </c>
       <c r="I34" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="L34" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="M34">
         <v>111</v>
@@ -24714,7 +24792,7 @@
         <v>-8.128</v>
       </c>
       <c r="AE34" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF34">
         <v>0.007778</v>
@@ -24767,10 +24845,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C35" s="2">
         <v>45969.37033057871</v>
@@ -24791,16 +24869,16 @@
         <v>990</v>
       </c>
       <c r="I35" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="L35" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="M35">
         <v>104</v>
@@ -24857,7 +24935,7 @@
         <v>-8.22966667</v>
       </c>
       <c r="AE35" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF35">
         <v>-0.011111</v>
@@ -24910,10 +24988,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>45969.37067769676</v>
@@ -24934,16 +25012,16 @@
         <v>1020</v>
       </c>
       <c r="I36" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="L36" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="M36">
         <v>114</v>
@@ -25000,7 +25078,7 @@
         <v>-7.91466667</v>
       </c>
       <c r="AE36" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF36">
         <v>0.034444</v>
@@ -25053,10 +25131,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C37" s="2">
         <v>45969.37102490741</v>
@@ -25077,16 +25155,16 @@
         <v>1050</v>
       </c>
       <c r="I37" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="L37" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="M37">
         <v>115</v>
@@ -25143,7 +25221,7 @@
         <v>-7.559</v>
       </c>
       <c r="AE37" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF37">
         <v>0.038889</v>
@@ -25196,10 +25274,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>45969.37137259259</v>
@@ -25220,16 +25298,16 @@
         <v>1080</v>
       </c>
       <c r="I38" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="L38" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="M38">
         <v>111</v>
@@ -25286,7 +25364,7 @@
         <v>-7.53866667</v>
       </c>
       <c r="AE38" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF38">
         <v>0.002222</v>
@@ -25339,10 +25417,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2">
         <v>45969.37171916667</v>
@@ -25363,16 +25441,16 @@
         <v>1110</v>
       </c>
       <c r="I39" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="L39" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="M39">
         <v>108</v>
@@ -25429,7 +25507,7 @@
         <v>-7.56933333</v>
       </c>
       <c r="AE39" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF39">
         <v>-0.003333</v>
@@ -25482,10 +25560,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C40" s="2">
         <v>45969.37206644676</v>
@@ -25506,16 +25584,16 @@
         <v>1140</v>
       </c>
       <c r="I40" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="L40" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M40">
         <v>109</v>
@@ -25572,7 +25650,7 @@
         <v>-7.20333333</v>
       </c>
       <c r="AE40" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF40">
         <v>0.04</v>
@@ -25625,10 +25703,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C41" s="2">
         <v>45969.37241391204</v>
@@ -25649,16 +25727,16 @@
         <v>1170</v>
       </c>
       <c r="I41" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="M41">
         <v>109</v>
@@ -25715,7 +25793,7 @@
         <v>-7.00033333</v>
       </c>
       <c r="AE41" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF41">
         <v>0.022222</v>
@@ -25768,10 +25846,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C42" s="2">
         <v>45969.37276103009</v>
@@ -25792,16 +25870,16 @@
         <v>1200</v>
       </c>
       <c r="I42" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L42" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="M42">
         <v>110</v>
@@ -25858,7 +25936,7 @@
         <v>-6.94933333</v>
       </c>
       <c r="AE42" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF42">
         <v>0.005556</v>
@@ -25911,10 +25989,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C43" s="2">
         <v>45969.37310821759</v>
@@ -25935,16 +26013,16 @@
         <v>1230</v>
       </c>
       <c r="I43" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="L43" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M43">
         <v>116</v>
@@ -26001,7 +26079,7 @@
         <v>-6.97</v>
       </c>
       <c r="AE43" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF43">
         <v>-0.002222</v>
@@ -26054,10 +26132,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2">
         <v>45969.3734556713</v>
@@ -26078,16 +26156,16 @@
         <v>1260</v>
       </c>
       <c r="I44" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="L44" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="M44">
         <v>121</v>
@@ -26144,7 +26222,7 @@
         <v>-6.89866667</v>
       </c>
       <c r="AE44" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF44">
         <v>0.007778</v>
@@ -26197,10 +26275,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2">
         <v>45969.37380241898</v>
@@ -26221,16 +26299,16 @@
         <v>1290</v>
       </c>
       <c r="I45" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="L45" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="M45">
         <v>118</v>
@@ -26287,7 +26365,7 @@
         <v>-6.82733333</v>
       </c>
       <c r="AE45" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF45">
         <v>0.007778</v>
@@ -26340,10 +26418,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2">
         <v>45969.37414959491</v>
@@ -26364,16 +26442,16 @@
         <v>1320</v>
       </c>
       <c r="I46" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="L46" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="M46">
         <v>116</v>
@@ -26430,7 +26508,7 @@
         <v>-6.77666667</v>
       </c>
       <c r="AE46" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF46">
         <v>0.005556</v>
@@ -26483,10 +26561,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2">
         <v>45969.37449711806</v>
@@ -26507,16 +26585,16 @@
         <v>1350</v>
       </c>
       <c r="I47" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="L47" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="M47">
         <v>117</v>
@@ -26573,7 +26651,7 @@
         <v>-6.736</v>
       </c>
       <c r="AE47" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF47">
         <v>0.004444</v>
@@ -26626,10 +26704,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2">
         <v>45969.37484409722</v>
@@ -26650,16 +26728,16 @@
         <v>1380</v>
       </c>
       <c r="I48" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L48" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="M48">
         <v>128</v>
@@ -26716,7 +26794,7 @@
         <v>-6.777</v>
       </c>
       <c r="AE48" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF48">
         <v>-0.004444</v>
@@ -26769,10 +26847,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C49" s="2">
         <v>45969.37519170139</v>
@@ -26793,16 +26871,16 @@
         <v>1410</v>
       </c>
       <c r="I49" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="L49" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="M49">
         <v>130</v>
@@ -26859,7 +26937,7 @@
         <v>-6.38033333</v>
       </c>
       <c r="AE49" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF49">
         <v>0.043333</v>
@@ -26912,10 +26990,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2">
         <v>45969.37553909722</v>
@@ -26936,16 +27014,16 @@
         <v>1440</v>
       </c>
       <c r="I50" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L50" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="M50">
         <v>126</v>
@@ -27002,7 +27080,7 @@
         <v>-6.44133333</v>
       </c>
       <c r="AE50" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF50">
         <v>-0.006667</v>
@@ -27055,10 +27133,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2">
         <v>45969.37588601852</v>
@@ -27079,16 +27157,16 @@
         <v>1470</v>
       </c>
       <c r="I51" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="L51" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="M51">
         <v>121</v>
@@ -27145,7 +27223,7 @@
         <v>-6.63466667</v>
       </c>
       <c r="AE51" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF51">
         <v>-0.021111</v>
@@ -27198,10 +27276,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2">
         <v>45969.3762328588</v>
@@ -27222,16 +27300,16 @@
         <v>1500</v>
       </c>
       <c r="I52" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="L52" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="M52">
         <v>113</v>
@@ -27288,7 +27366,7 @@
         <v>-6.25866667</v>
       </c>
       <c r="AE52" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF52">
         <v>0.041111</v>
@@ -27341,10 +27419,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2">
         <v>45969.37658040509</v>
@@ -27365,16 +27443,16 @@
         <v>1530</v>
       </c>
       <c r="I53" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="L53" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="M53">
         <v>122</v>
@@ -27431,7 +27509,7 @@
         <v>-6.37</v>
       </c>
       <c r="AE53" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF53">
         <v>-0.012222</v>
@@ -27484,10 +27562,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C54" s="2">
         <v>45969.37692777778</v>
@@ -27508,16 +27586,16 @@
         <v>1560</v>
       </c>
       <c r="I54" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="L54" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="M54">
         <v>128</v>
@@ -27574,7 +27652,7 @@
         <v>-6.269</v>
       </c>
       <c r="AE54" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF54">
         <v>0.011111</v>
@@ -27627,10 +27705,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2">
         <v>45969.37727483796</v>
@@ -27651,16 +27729,16 @@
         <v>1590</v>
       </c>
       <c r="I55" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="L55" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="M55">
         <v>129</v>
@@ -27717,7 +27795,7 @@
         <v>-6.08566667</v>
       </c>
       <c r="AE55" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF55">
         <v>0.02</v>
@@ -27770,10 +27848,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C56" s="2">
         <v>45969.37762207176</v>
@@ -27794,16 +27872,16 @@
         <v>1620</v>
       </c>
       <c r="I56" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="M56">
         <v>134</v>
@@ -27860,7 +27938,7 @@
         <v>-6.12666667</v>
       </c>
       <c r="AE56" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF56">
         <v>-0.004444</v>
@@ -27913,10 +27991,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C57" s="2">
         <v>45969.37796931713</v>
@@ -27937,16 +28015,16 @@
         <v>1650</v>
       </c>
       <c r="I57" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="L57" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M57">
         <v>131</v>
@@ -28003,7 +28081,7 @@
         <v>-5.87233333</v>
       </c>
       <c r="AE57" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF57">
         <v>0.027778</v>
@@ -28056,10 +28134,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C58" s="2">
         <v>45969.378316875</v>
@@ -28080,16 +28158,16 @@
         <v>1680</v>
       </c>
       <c r="I58" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="L58" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="M58">
         <v>126</v>
@@ -28146,7 +28224,7 @@
         <v>-6.00466667</v>
       </c>
       <c r="AE58" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF58">
         <v>-0.014444</v>
@@ -28199,10 +28277,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C59" s="2">
         <v>45969.37866390046</v>
@@ -28223,16 +28301,16 @@
         <v>1710</v>
       </c>
       <c r="I59" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="L59" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M59">
         <v>126</v>
@@ -28289,7 +28367,7 @@
         <v>-6.08566667</v>
       </c>
       <c r="AE59" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF59">
         <v>-0.008888999999999999</v>
@@ -28342,10 +28420,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C60" s="2">
         <v>45969.37901099537</v>
@@ -28366,16 +28444,16 @@
         <v>1740</v>
       </c>
       <c r="I60" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="L60" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="M60">
         <v>130</v>
@@ -28432,7 +28510,7 @@
         <v>-6.06566667</v>
       </c>
       <c r="AE60" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF60">
         <v>0.002222</v>
@@ -28485,10 +28563,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C61" s="2">
         <v>45969.3793580787</v>
@@ -28509,16 +28587,16 @@
         <v>1770</v>
       </c>
       <c r="I61" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="L61" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="M61">
         <v>125</v>
@@ -28575,7 +28653,7 @@
         <v>-6.06533333</v>
       </c>
       <c r="AE61" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF61">
         <v>0</v>
@@ -28628,10 +28706,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2">
         <v>45969.37970578704</v>
@@ -28652,16 +28730,16 @@
         <v>1800</v>
       </c>
       <c r="I62" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="L62" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="M62">
         <v>124</v>
@@ -28718,7 +28796,7 @@
         <v>-6.025</v>
       </c>
       <c r="AE62" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF62">
         <v>0.004444</v>
@@ -28771,10 +28849,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C63" s="2">
         <v>45969.38005290509</v>
@@ -28795,16 +28873,16 @@
         <v>1830</v>
       </c>
       <c r="I63" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="L63" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="M63">
         <v>122</v>
@@ -28861,7 +28939,7 @@
         <v>-5.93333333</v>
       </c>
       <c r="AE63" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF63">
         <v>0.01</v>
@@ -28914,10 +28992,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2">
         <v>45969.38040023148</v>
@@ -28938,16 +29016,16 @@
         <v>1860</v>
       </c>
       <c r="I64" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="L64" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="M64">
         <v>136</v>
@@ -29004,7 +29082,7 @@
         <v>-6.13666667</v>
       </c>
       <c r="AE64" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF64">
         <v>-0.022222</v>
@@ -29057,10 +29135,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C65" s="2">
         <v>45969.380746875</v>
@@ -29081,16 +29159,16 @@
         <v>1890</v>
       </c>
       <c r="I65" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="L65" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="M65">
         <v>128</v>
@@ -29147,7 +29225,7 @@
         <v>-6.16733333</v>
       </c>
       <c r="AE65" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF65">
         <v>-0.003333</v>
@@ -29200,10 +29278,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C66" s="2">
         <v>45969.38109409723</v>
@@ -29224,16 +29302,16 @@
         <v>1920</v>
       </c>
       <c r="I66" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="L66" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="M66">
         <v>136</v>
@@ -29290,7 +29368,7 @@
         <v>-6.20766667</v>
       </c>
       <c r="AE66" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF66">
         <v>-0.004444</v>
@@ -29343,10 +29421,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>45969.38139638889</v>
@@ -29367,16 +29445,16 @@
         <v>1943</v>
       </c>
       <c r="I67" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="L67" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="M67">
         <v>130</v>
@@ -29433,7 +29511,7 @@
         <v>-1.31146914</v>
       </c>
       <c r="AE67" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF67">
         <v>0.003966</v>
@@ -29486,10 +29564,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2">
         <v>45969.38144174768</v>
@@ -29510,16 +29588,16 @@
         <v>1950</v>
       </c>
       <c r="I68" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="L68" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M68">
         <v>132</v>
@@ -29576,7 +29654,7 @@
         <v>-6.035</v>
       </c>
       <c r="AE68" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF68">
         <v>-0.516576</v>
@@ -29629,10 +29707,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C69" s="2">
         <v>45969.38178854166</v>
@@ -29653,16 +29731,16 @@
         <v>1980</v>
       </c>
       <c r="I69" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="L69" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="M69">
         <v>139</v>
@@ -29719,7 +29797,7 @@
         <v>-5.76066667</v>
       </c>
       <c r="AE69" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF69">
         <v>0.03</v>
@@ -29772,10 +29850,10 @@
     </row>
     <row r="70" spans="1:47">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C70" s="2">
         <v>45969.38210657408</v>
@@ -29796,16 +29874,16 @@
         <v>2003</v>
       </c>
       <c r="I70" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="L70" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="M70">
         <v>134</v>
@@ -29862,7 +29940,7 @@
         <v>-5.73533333</v>
       </c>
       <c r="AE70" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF70">
         <v>0.001389</v>
@@ -29915,10 +29993,10 @@
     </row>
     <row r="71" spans="1:47">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C71" s="2">
         <v>45969.38213609954</v>
@@ -29939,16 +30017,16 @@
         <v>2010</v>
       </c>
       <c r="I71" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="L71" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="M71">
         <v>133</v>
@@ -30005,7 +30083,7 @@
         <v>-5.54733333</v>
       </c>
       <c r="AE71" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF71">
         <v>0.020556</v>
@@ -30058,10 +30136,10 @@
     </row>
     <row r="72" spans="1:47">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C72" s="2">
         <v>45969.38248739584</v>
@@ -30082,16 +30160,16 @@
         <v>2040</v>
       </c>
       <c r="I72" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="L72" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="M72">
         <v>122</v>
@@ -30148,7 +30226,7 @@
         <v>-5.466</v>
       </c>
       <c r="AE72" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF72">
         <v>0.008888999999999999</v>
@@ -30201,10 +30279,10 @@
     </row>
     <row r="73" spans="1:47">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2">
         <v>45969.38280052083</v>
@@ -30225,16 +30303,16 @@
         <v>2063</v>
       </c>
       <c r="I73" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="L73" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="M73">
         <v>130</v>
@@ -30291,7 +30369,7 @@
         <v>-5.41516667</v>
       </c>
       <c r="AE73" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF73">
         <v>0.002778</v>
@@ -30344,10 +30422,10 @@
     </row>
     <row r="74" spans="1:47">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C74" s="2">
         <v>45969.38283481482</v>
@@ -30368,16 +30446,16 @@
         <v>2070</v>
       </c>
       <c r="I74" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="L74" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="M74">
         <v>132</v>
@@ -30434,7 +30512,7 @@
         <v>-5.36466667</v>
       </c>
       <c r="AE74" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF74">
         <v>0.005556</v>
@@ -30487,10 +30565,10 @@
     </row>
     <row r="75" spans="1:47">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C75" s="2">
         <v>45969.38318189815</v>
@@ -30511,16 +30589,16 @@
         <v>2100</v>
       </c>
       <c r="I75" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="L75" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M75">
         <v>130</v>
@@ -30577,7 +30655,7 @@
         <v>-5.50666667</v>
       </c>
       <c r="AE75" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF75">
         <v>-0.015556</v>
@@ -30630,10 +30708,10 @@
     </row>
     <row r="76" spans="1:47">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C76" s="2">
         <v>45969.38348363426</v>
@@ -30654,16 +30732,16 @@
         <v>2123</v>
       </c>
       <c r="I76" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="L76" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="M76">
         <v>142</v>
@@ -30720,7 +30798,7 @@
         <v>-5.43566667</v>
       </c>
       <c r="AE76" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF76">
         <v>0.003889</v>
@@ -30773,10 +30851,10 @@
     </row>
     <row r="77" spans="1:47">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C77" s="2">
         <v>45969.38352966435</v>
@@ -30797,16 +30875,16 @@
         <v>2130</v>
       </c>
       <c r="I77" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="L77" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="M77">
         <v>140</v>
@@ -30863,7 +30941,7 @@
         <v>-5.31366667</v>
       </c>
       <c r="AE77" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF77">
         <v>0.013333</v>
@@ -30916,10 +30994,10 @@
     </row>
     <row r="78" spans="1:47">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C78" s="2">
         <v>45969.3838778588</v>
@@ -30940,16 +31018,16 @@
         <v>2160</v>
       </c>
       <c r="I78" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="L78" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="M78">
         <v>141</v>
@@ -31006,7 +31084,7 @@
         <v>-4.97833333</v>
       </c>
       <c r="AE78" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF78">
         <v>0.036667</v>
@@ -31059,10 +31137,10 @@
     </row>
     <row r="79" spans="1:47">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2">
         <v>45969.38417993056</v>
@@ -31083,16 +31161,16 @@
         <v>2183</v>
       </c>
       <c r="I79" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="L79" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="M79">
         <v>144</v>
@@ -31149,7 +31227,7 @@
         <v>-4.8565</v>
       </c>
       <c r="AE79" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF79">
         <v>0.006667</v>
@@ -31202,10 +31280,10 @@
     </row>
     <row r="80" spans="1:47">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2">
         <v>45969.38422498843</v>
@@ -31226,16 +31304,16 @@
         <v>2190</v>
       </c>
       <c r="I80" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="L80" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="M80">
         <v>144</v>
@@ -31292,7 +31370,7 @@
         <v>-4.71433333</v>
       </c>
       <c r="AE80" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF80">
         <v>0.015556</v>
@@ -31345,10 +31423,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C81" s="2">
         <v>45969.38457288194</v>
@@ -31369,16 +31447,16 @@
         <v>2220</v>
       </c>
       <c r="I81" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="L81" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="M81">
         <v>146</v>
@@ -31435,7 +31513,7 @@
         <v>-4.55166667</v>
       </c>
       <c r="AE81" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF81">
         <v>0.017778</v>
@@ -31488,10 +31566,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2">
         <v>45969.38487384259</v>
@@ -31512,16 +31590,16 @@
         <v>2243</v>
       </c>
       <c r="I82" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="L82" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="M82">
         <v>142</v>
@@ -31578,7 +31656,7 @@
         <v>-4.37383333</v>
       </c>
       <c r="AE82" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF82">
         <v>0.009722</v>
@@ -31631,10 +31709,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2">
         <v>45969.38492042824</v>
@@ -31655,16 +31733,16 @@
         <v>2250</v>
       </c>
       <c r="I83" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="L83" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="M83">
         <v>150</v>
@@ -31721,7 +31799,7 @@
         <v>-4.10466667</v>
       </c>
       <c r="AE83" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF83">
         <v>0.029444</v>
@@ -31774,10 +31852,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2">
         <v>45969.38519724537</v>
@@ -31798,16 +31876,16 @@
         <v>2273</v>
       </c>
       <c r="I84" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L84" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="M84">
         <v>141</v>
@@ -31864,7 +31942,7 @@
         <v>-4.27733333</v>
       </c>
       <c r="AE84" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF84">
         <v>-0.018889</v>
@@ -31917,10 +31995,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C85" s="2">
         <v>45969.38526693287</v>
@@ -31941,16 +32019,16 @@
         <v>2280</v>
       </c>
       <c r="I85" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="L85" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="M85">
         <v>149</v>
@@ -32007,7 +32085,7 @@
         <v>-4.22666667</v>
       </c>
       <c r="AE85" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF85">
         <v>0.005556</v>
@@ -32060,10 +32138,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C86" s="2">
         <v>45969.38556775463</v>
@@ -32084,16 +32162,16 @@
         <v>2303</v>
       </c>
       <c r="I86" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="L86" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="M86">
         <v>152</v>
@@ -32150,7 +32228,7 @@
         <v>-4.247</v>
       </c>
       <c r="AE86" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF86">
         <v>-0.002222</v>
@@ -32203,10 +32281,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C87" s="2">
         <v>45969.38561557871</v>
@@ -32227,16 +32305,16 @@
         <v>2310</v>
       </c>
       <c r="I87" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="L87" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="M87">
         <v>148</v>
@@ -32293,7 +32371,7 @@
         <v>-4.33833333</v>
       </c>
       <c r="AE87" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF87">
         <v>-0.01</v>
@@ -32346,10 +32424,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C88" s="2">
         <v>45969.38626327546</v>
@@ -32370,16 +32448,16 @@
         <v>2363</v>
       </c>
       <c r="I88" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="L88" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="M88">
         <v>182</v>
@@ -32436,7 +32514,7 @@
         <v>-4.6735</v>
       </c>
       <c r="AE88" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF88">
         <v>-0.018333</v>
@@ -32489,10 +32567,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C89" s="2">
         <v>45969.38631001157</v>
@@ -32513,16 +32591,16 @@
         <v>2370</v>
       </c>
       <c r="I89" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="L89" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="M89">
         <v>180</v>
@@ -32579,7 +32657,7 @@
         <v>-4.75483333</v>
       </c>
       <c r="AE89" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF89">
         <v>-0.004444</v>
@@ -32632,10 +32710,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C90" s="2">
         <v>45969.38665728009</v>
@@ -32656,16 +32734,16 @@
         <v>2400</v>
       </c>
       <c r="I90" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="L90" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="M90">
         <v>170</v>
@@ -32722,7 +32800,7 @@
         <v>-5.19166667</v>
       </c>
       <c r="AE90" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF90">
         <v>-0.047778</v>
@@ -32775,10 +32853,10 @@
     </row>
     <row r="91" spans="1:47">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2">
         <v>45969.38695730324</v>
@@ -32799,16 +32877,16 @@
         <v>2423</v>
       </c>
       <c r="I91" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="L91" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="M91">
         <v>177</v>
@@ -32865,7 +32943,7 @@
         <v>-5.09016667</v>
       </c>
       <c r="AE91" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF91">
         <v>0.005556</v>
@@ -32918,10 +32996,10 @@
     </row>
     <row r="92" spans="1:47">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C92" s="2">
         <v>45969.38700427084</v>
@@ -32942,16 +33020,16 @@
         <v>2430</v>
       </c>
       <c r="I92" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="L92" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="M92">
         <v>166</v>
@@ -33008,7 +33086,7 @@
         <v>-4.97833333</v>
       </c>
       <c r="AE92" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF92">
         <v>0.012222</v>
@@ -33061,10 +33139,10 @@
     </row>
     <row r="93" spans="1:47">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C93" s="2">
         <v>45969.3873515162</v>
@@ -33085,16 +33163,16 @@
         <v>2460</v>
       </c>
       <c r="I93" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="L93" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="M93">
         <v>180</v>
@@ -33151,7 +33229,7 @@
         <v>-5.36466667</v>
       </c>
       <c r="AE93" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF93">
         <v>-0.042222</v>
@@ -33204,10 +33282,10 @@
     </row>
     <row r="94" spans="1:47">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C94" s="2">
         <v>45969.38766517361</v>
@@ -33228,16 +33306,16 @@
         <v>2483</v>
       </c>
       <c r="I94" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="L94" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="M94">
         <v>178</v>
@@ -33294,7 +33372,7 @@
         <v>-4.70416667</v>
       </c>
       <c r="AE94" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF94">
         <v>0.036111</v>
@@ -33347,10 +33425,10 @@
     </row>
     <row r="95" spans="1:47">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C95" s="2">
         <v>45969.38769974537</v>
@@ -33371,16 +33449,16 @@
         <v>2490</v>
       </c>
       <c r="I95" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="L95" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="M95">
         <v>156</v>
@@ -33437,7 +33515,7 @@
         <v>-3.69833333</v>
       </c>
       <c r="AE95" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF95">
         <v>0.11</v>
@@ -33490,10 +33568,10 @@
     </row>
     <row r="96" spans="1:47">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C96" s="2">
         <v>45969.38797651621</v>
@@ -33514,16 +33592,16 @@
         <v>2513</v>
       </c>
       <c r="I96" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="L96" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="M96">
         <v>142</v>
@@ -33580,7 +33658,7 @@
         <v>-3.26133333</v>
       </c>
       <c r="AE96" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF96">
         <v>0.047778</v>
@@ -33633,10 +33711,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2">
         <v>45969.38834788195</v>
@@ -33657,16 +33735,16 @@
         <v>2543</v>
       </c>
       <c r="I97" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="L97" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="M97">
         <v>146</v>
@@ -33723,7 +33801,7 @@
         <v>-4.379</v>
       </c>
       <c r="AE97" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF97">
         <v>-0.122222</v>
@@ -33776,10 +33854,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C98" s="2">
         <v>45969.38839309028</v>
@@ -33800,16 +33878,16 @@
         <v>2550</v>
       </c>
       <c r="I98" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="L98" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="M98">
         <v>156</v>
@@ -33866,7 +33944,7 @@
         <v>-4.003</v>
       </c>
       <c r="AE98" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF98">
         <v>0.020556</v>
@@ -33919,10 +33997,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C99" s="2">
         <v>45969.38877582176</v>
@@ -33943,16 +34021,16 @@
         <v>2580</v>
       </c>
       <c r="I99" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="L99" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="M99">
         <v>140</v>
@@ -34009,7 +34087,7 @@
         <v>-4.91733333</v>
       </c>
       <c r="AE99" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AF99">
         <v>-0.1</v>
